--- a/nablarch_sample/アプリケーション方式設計書_3画面処理方式_3.1同期処理方式.xlsx
+++ b/nablarch_sample/アプリケーション方式設計書_3画面処理方式_3.1同期処理方式.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24931"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26731"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F10FA1A0-82A4-4E0A-89C1-8094138A4967}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB1EAFF9-996A-4E6D-9EC7-2263D852D581}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1155" yWindow="-120" windowWidth="27765" windowHeight="16440" tabRatio="668" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" tabRatio="668" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="3.1.同期処理方式" sheetId="2" r:id="rId1"/>
@@ -2705,10 +2705,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>https://nablarch.github.io/docs/5u21/doc/application_framework/application_framework/handlers/web/secure_handler.html</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>ユーザの利便性向上につながる。</t>
     <rPh sb="4" eb="7">
       <t>リベンセイ</t>
@@ -2836,10 +2832,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>https://nablarch.github.io/docs/5u21/doc/application_framework/application_framework/web_service/rest/index.html</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>クライアント側では、入力候補の取得はAjaxを用いて非同期で行うこととする。</t>
     <rPh sb="6" eb="7">
       <t>ガワ</t>
@@ -3388,6 +3380,14 @@
   </si>
   <si>
     <t>ログ出力内容の詳細は「7.13.ログ」を参照。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://nablarch.github.io/docs/6u2/doc/application_framework/application_framework/handlers/web/secure_handler.html</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://nablarch.github.io/docs/6u2/doc/application_framework/application_framework/web_service/rest/index.html</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -3398,7 +3398,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="yyyy/mm/dd"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3463,6 +3463,15 @@
     <font>
       <u/>
       <sz val="11"/>
+      <color theme="10"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="9"/>
       <color theme="10"/>
       <name val="ＭＳ Ｐゴシック"/>
       <family val="2"/>
@@ -4032,12 +4041,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="7" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -4103,6 +4106,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="7" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="7" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="8">
@@ -4162,8 +4171,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="1362075" y="44084599"/>
-          <a:ext cx="7810499" cy="787676"/>
+          <a:off x="1266825" y="43109874"/>
+          <a:ext cx="7172324" cy="768626"/>
           <a:chOff x="1362075" y="5760869"/>
           <a:chExt cx="7810499" cy="820906"/>
         </a:xfrm>
@@ -5018,146 +5027,146 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AI370"/>
-  <sheetFormatPr defaultColWidth="3.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="3.6328125" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="3.625" style="4"/>
+    <col min="1" max="16384" width="3.6328125" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="3"/>
-      <c r="E1" s="114" t="s">
+      <c r="E1" s="112" t="s">
         <v>156</v>
       </c>
-      <c r="F1" s="115"/>
-      <c r="G1" s="115"/>
-      <c r="H1" s="115"/>
-      <c r="I1" s="115"/>
-      <c r="J1" s="115"/>
-      <c r="K1" s="115"/>
-      <c r="L1" s="115"/>
-      <c r="M1" s="115"/>
-      <c r="N1" s="115"/>
-      <c r="O1" s="116"/>
+      <c r="F1" s="113"/>
+      <c r="G1" s="113"/>
+      <c r="H1" s="113"/>
+      <c r="I1" s="113"/>
+      <c r="J1" s="113"/>
+      <c r="K1" s="113"/>
+      <c r="L1" s="113"/>
+      <c r="M1" s="113"/>
+      <c r="N1" s="113"/>
+      <c r="O1" s="114"/>
       <c r="P1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="Q1" s="2"/>
-      <c r="R1" s="117" t="s">
+      <c r="R1" s="115" t="s">
         <v>155</v>
       </c>
-      <c r="S1" s="118"/>
-      <c r="T1" s="118"/>
-      <c r="U1" s="118"/>
-      <c r="V1" s="118"/>
-      <c r="W1" s="118"/>
-      <c r="X1" s="119"/>
+      <c r="S1" s="116"/>
+      <c r="T1" s="116"/>
+      <c r="U1" s="116"/>
+      <c r="V1" s="116"/>
+      <c r="W1" s="116"/>
+      <c r="X1" s="117"/>
       <c r="Y1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="Z1" s="3"/>
-      <c r="AA1" s="120"/>
-      <c r="AB1" s="121"/>
-      <c r="AC1" s="121"/>
-      <c r="AD1" s="121"/>
-      <c r="AE1" s="122"/>
-      <c r="AF1" s="111"/>
-      <c r="AG1" s="112"/>
-      <c r="AH1" s="112"/>
-      <c r="AI1" s="113"/>
-    </row>
-    <row r="2" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AA1" s="118"/>
+      <c r="AB1" s="119"/>
+      <c r="AC1" s="119"/>
+      <c r="AD1" s="119"/>
+      <c r="AE1" s="120"/>
+      <c r="AF1" s="109"/>
+      <c r="AG1" s="110"/>
+      <c r="AH1" s="110"/>
+      <c r="AI1" s="111"/>
+    </row>
+    <row r="2" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
       <c r="D2" s="7"/>
-      <c r="E2" s="123"/>
-      <c r="F2" s="124"/>
-      <c r="G2" s="124"/>
-      <c r="H2" s="124"/>
-      <c r="I2" s="124"/>
-      <c r="J2" s="124"/>
-      <c r="K2" s="124"/>
-      <c r="L2" s="124"/>
-      <c r="M2" s="124"/>
-      <c r="N2" s="124"/>
-      <c r="O2" s="125"/>
+      <c r="E2" s="121"/>
+      <c r="F2" s="122"/>
+      <c r="G2" s="122"/>
+      <c r="H2" s="122"/>
+      <c r="I2" s="122"/>
+      <c r="J2" s="122"/>
+      <c r="K2" s="122"/>
+      <c r="L2" s="122"/>
+      <c r="M2" s="122"/>
+      <c r="N2" s="122"/>
+      <c r="O2" s="123"/>
       <c r="P2" s="8" t="s">
         <v>12</v>
       </c>
       <c r="Q2" s="9"/>
-      <c r="R2" s="126" t="s">
+      <c r="R2" s="124" t="s">
         <v>3</v>
       </c>
-      <c r="S2" s="127"/>
-      <c r="T2" s="127"/>
-      <c r="U2" s="127"/>
-      <c r="V2" s="127"/>
-      <c r="W2" s="127"/>
-      <c r="X2" s="128"/>
+      <c r="S2" s="125"/>
+      <c r="T2" s="125"/>
+      <c r="U2" s="125"/>
+      <c r="V2" s="125"/>
+      <c r="W2" s="125"/>
+      <c r="X2" s="126"/>
       <c r="Y2" s="1" t="s">
         <v>4</v>
       </c>
       <c r="Z2" s="3"/>
-      <c r="AA2" s="120"/>
-      <c r="AB2" s="121"/>
-      <c r="AC2" s="121"/>
-      <c r="AD2" s="121"/>
-      <c r="AE2" s="122"/>
-      <c r="AF2" s="111"/>
-      <c r="AG2" s="112"/>
-      <c r="AH2" s="112"/>
-      <c r="AI2" s="113"/>
-    </row>
-    <row r="3" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AA2" s="118"/>
+      <c r="AB2" s="119"/>
+      <c r="AC2" s="119"/>
+      <c r="AD2" s="119"/>
+      <c r="AE2" s="120"/>
+      <c r="AF2" s="109"/>
+      <c r="AG2" s="110"/>
+      <c r="AH2" s="110"/>
+      <c r="AI2" s="111"/>
+    </row>
+    <row r="3" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B3" s="10"/>
       <c r="C3" s="11"/>
       <c r="D3" s="3"/>
-      <c r="E3" s="132"/>
-      <c r="F3" s="132"/>
-      <c r="G3" s="132"/>
-      <c r="H3" s="132"/>
-      <c r="I3" s="132"/>
-      <c r="J3" s="132"/>
-      <c r="K3" s="132"/>
-      <c r="L3" s="132"/>
-      <c r="M3" s="132"/>
-      <c r="N3" s="132"/>
-      <c r="O3" s="132"/>
+      <c r="E3" s="130"/>
+      <c r="F3" s="130"/>
+      <c r="G3" s="130"/>
+      <c r="H3" s="130"/>
+      <c r="I3" s="130"/>
+      <c r="J3" s="130"/>
+      <c r="K3" s="130"/>
+      <c r="L3" s="130"/>
+      <c r="M3" s="130"/>
+      <c r="N3" s="130"/>
+      <c r="O3" s="130"/>
       <c r="P3" s="12"/>
       <c r="Q3" s="13"/>
-      <c r="R3" s="129"/>
-      <c r="S3" s="130"/>
-      <c r="T3" s="130"/>
-      <c r="U3" s="130"/>
-      <c r="V3" s="130"/>
-      <c r="W3" s="130"/>
-      <c r="X3" s="131"/>
+      <c r="R3" s="127"/>
+      <c r="S3" s="128"/>
+      <c r="T3" s="128"/>
+      <c r="U3" s="128"/>
+      <c r="V3" s="128"/>
+      <c r="W3" s="128"/>
+      <c r="X3" s="129"/>
       <c r="Y3" s="12" t="s">
         <v>6</v>
       </c>
       <c r="Z3" s="14"/>
-      <c r="AA3" s="120"/>
-      <c r="AB3" s="121"/>
-      <c r="AC3" s="121"/>
-      <c r="AD3" s="121"/>
-      <c r="AE3" s="122"/>
-      <c r="AF3" s="111"/>
-      <c r="AG3" s="112"/>
-      <c r="AH3" s="112"/>
-      <c r="AI3" s="113"/>
-    </row>
-    <row r="4" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="5" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AA3" s="118"/>
+      <c r="AB3" s="119"/>
+      <c r="AC3" s="119"/>
+      <c r="AD3" s="119"/>
+      <c r="AE3" s="120"/>
+      <c r="AF3" s="109"/>
+      <c r="AG3" s="110"/>
+      <c r="AH3" s="110"/>
+      <c r="AI3" s="111"/>
+    </row>
+    <row r="4" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="5" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B5" s="15" t="s">
         <v>13</v>
       </c>
@@ -5165,8 +5174,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="7" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="7" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C7" s="15" t="str">
         <f>$B$5&amp;"1."</f>
         <v>3.1.</v>
@@ -5175,8 +5184,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="9" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="9" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D9" s="28" t="str">
         <f>$C$7&amp;"1."</f>
         <v>3.1.1.</v>
@@ -5185,19 +5194,19 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D10" s="15"/>
       <c r="E10" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D11" s="42"/>
       <c r="E11" s="41" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="12" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="12" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D12" s="26"/>
       <c r="E12" s="26"/>
       <c r="F12" s="26"/>
@@ -5231,7 +5240,7 @@
       <c r="AH12" s="26"/>
       <c r="AI12" s="26"/>
     </row>
-    <row r="13" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D13" s="15" t="str">
         <f>$C$7&amp;"2."</f>
         <v>3.1.2.</v>
@@ -5270,7 +5279,7 @@
       <c r="AH13" s="27"/>
       <c r="AI13" s="27"/>
     </row>
-    <row r="14" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B14" s="41"/>
       <c r="E14" s="42" t="str">
         <f>D13&amp;"1."</f>
@@ -5310,7 +5319,7 @@
       <c r="AH14" s="27"/>
       <c r="AI14" s="27"/>
     </row>
-    <row r="15" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D15" s="29"/>
       <c r="E15" s="29"/>
       <c r="F15" s="52" t="s">
@@ -5348,7 +5357,7 @@
       <c r="AH15" s="29"/>
       <c r="AI15" s="29"/>
     </row>
-    <row r="16" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D16" s="29"/>
       <c r="E16" s="29"/>
       <c r="F16" s="56" t="s">
@@ -5386,7 +5395,7 @@
       <c r="AH16" s="29"/>
       <c r="AI16" s="29"/>
     </row>
-    <row r="17" spans="4:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="4:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D17" s="29"/>
       <c r="E17" s="29"/>
       <c r="F17" s="35" t="s">
@@ -5424,7 +5433,7 @@
       <c r="AH17" s="29"/>
       <c r="AI17" s="29"/>
     </row>
-    <row r="18" spans="4:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="4:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D18" s="29"/>
       <c r="E18" s="29"/>
       <c r="F18" s="30"/>
@@ -5452,7 +5461,7 @@
       <c r="AH18" s="29"/>
       <c r="AI18" s="29"/>
     </row>
-    <row r="19" spans="4:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="4:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D19" s="29"/>
       <c r="E19" s="29"/>
       <c r="F19" s="32"/>
@@ -5488,7 +5497,7 @@
       <c r="AH19" s="29"/>
       <c r="AI19" s="29"/>
     </row>
-    <row r="20" spans="4:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="4:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D20" s="42"/>
       <c r="F20" s="27"/>
       <c r="G20" s="27"/>
@@ -5521,8 +5530,8 @@
       <c r="AH20" s="27"/>
       <c r="AI20" s="27"/>
     </row>
-    <row r="21" spans="4:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="22" spans="4:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="4:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="22" spans="4:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D22" s="28" t="str">
         <f>$C$7&amp;"3."</f>
         <v>3.1.3.</v>
@@ -5531,7 +5540,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="4:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="4:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D23" s="28"/>
       <c r="E23" s="28" t="str">
         <f>$D$22&amp;"1."</f>
@@ -5542,28 +5551,28 @@
         <v>ブラウザキャッシュ制御機能概要</v>
       </c>
     </row>
-    <row r="24" spans="4:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="4:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F24" s="4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="25" spans="4:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="4:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F25" s="41" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="26" spans="4:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="4:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F26" s="36" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="27" spans="4:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="4:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F27" s="36" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="28" spans="4:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="29" spans="4:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="4:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="29" spans="4:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E29" s="28" t="str">
         <f>$D$22&amp;"2."</f>
         <v>3.1.3.2.</v>
@@ -5573,7 +5582,7 @@
         <v>ブラウザキャッシュ制御手段</v>
       </c>
     </row>
-    <row r="30" spans="4:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="4:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F30" s="16" t="s">
         <v>47</v>
       </c>
@@ -5608,7 +5617,7 @@
       <c r="AG30" s="53"/>
       <c r="AH30" s="54"/>
     </row>
-    <row r="31" spans="4:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="4:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F31" s="56" t="s">
         <v>51</v>
       </c>
@@ -5643,7 +5652,7 @@
       <c r="AG31" s="68"/>
       <c r="AH31" s="95"/>
     </row>
-    <row r="32" spans="4:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="4:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F32" s="35" t="s">
         <v>242</v>
       </c>
@@ -5678,7 +5687,7 @@
       <c r="AG32" s="98"/>
       <c r="AH32" s="100"/>
     </row>
-    <row r="33" spans="4:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="4:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F33" s="32"/>
       <c r="G33" s="33"/>
       <c r="H33" s="33"/>
@@ -5711,7 +5720,7 @@
       <c r="AG33" s="101"/>
       <c r="AH33" s="102"/>
     </row>
-    <row r="34" spans="4:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="4:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F34" s="55"/>
       <c r="G34" s="55"/>
       <c r="H34" s="55"/>
@@ -5742,7 +5751,7 @@
       <c r="AG34" s="55"/>
       <c r="AH34" s="55"/>
     </row>
-    <row r="35" spans="4:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="4:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E35" s="24" t="str">
         <f>$D$22&amp;"3."</f>
         <v>3.1.3.3.</v>
@@ -5751,44 +5760,44 @@
         <v>216</v>
       </c>
     </row>
-    <row r="36" spans="4:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="4:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E36" s="24"/>
       <c r="F36" s="74" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="37" spans="4:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="4:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E37" s="24"/>
       <c r="F37" s="29" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="38" spans="4:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="4:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E38" s="24"/>
     </row>
-    <row r="39" spans="4:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="4:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E39" s="24"/>
       <c r="F39" s="29" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="40" spans="4:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="4:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E40" s="24"/>
       <c r="F40" s="29" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="41" spans="4:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="4:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E41" s="24"/>
     </row>
-    <row r="42" spans="4:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="4:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E42" s="24"/>
-      <c r="F42" s="109" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="43" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="44" spans="4:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F42" s="131" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="43" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="44" spans="4:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D44" s="66" t="str">
         <f>$C$7&amp;"4."</f>
         <v>3.1.4.</v>
@@ -5797,7 +5806,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="45" spans="4:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="4:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D45" s="66"/>
       <c r="E45" s="66" t="str">
         <f>$D$44&amp;"1."</f>
@@ -5808,13 +5817,13 @@
         <v>オートコンプリート機能概要</v>
       </c>
     </row>
-    <row r="46" spans="4:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="4:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F46" s="36" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="47" spans="4:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="48" spans="4:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="4:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="48" spans="4:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E48" s="66" t="str">
         <f>$D$44&amp;"2."</f>
         <v>3.1.4.2.</v>
@@ -5824,12 +5833,12 @@
         <v>オートコンプリート方法</v>
       </c>
     </row>
-    <row r="49" spans="5:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="5:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F49" s="36" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="50" spans="5:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="5:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F50" s="52" t="s">
         <v>18</v>
       </c>
@@ -5864,7 +5873,7 @@
       <c r="AG50" s="53"/>
       <c r="AH50" s="54"/>
     </row>
-    <row r="51" spans="5:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="5:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F51" s="69" t="s">
         <v>17</v>
       </c>
@@ -5899,7 +5908,7 @@
       <c r="AG51" s="98"/>
       <c r="AH51" s="100"/>
     </row>
-    <row r="52" spans="5:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="5:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F52" s="81"/>
       <c r="G52" s="101"/>
       <c r="H52" s="101"/>
@@ -5932,7 +5941,7 @@
       <c r="AG52" s="101"/>
       <c r="AH52" s="102"/>
     </row>
-    <row r="53" spans="5:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="5:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F53" s="103" t="s">
         <v>16</v>
       </c>
@@ -5967,7 +5976,7 @@
       <c r="AG53" s="70"/>
       <c r="AH53" s="94"/>
     </row>
-    <row r="54" spans="5:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="5:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F54" s="103"/>
       <c r="G54" s="70"/>
       <c r="H54" s="70"/>
@@ -6000,7 +6009,7 @@
       <c r="AG54" s="70"/>
       <c r="AH54" s="94"/>
     </row>
-    <row r="55" spans="5:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="5:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F55" s="81"/>
       <c r="G55" s="101"/>
       <c r="H55" s="101"/>
@@ -6033,8 +6042,8 @@
       <c r="AG55" s="101"/>
       <c r="AH55" s="102"/>
     </row>
-    <row r="56" spans="5:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="57" spans="5:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="5:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="57" spans="5:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E57" s="66" t="str">
         <f>$D$44&amp;"3."</f>
         <v>3.1.4.3.</v>
@@ -6043,76 +6052,76 @@
         <v>216</v>
       </c>
     </row>
-    <row r="58" spans="5:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="5:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E58" s="66"/>
       <c r="F58" s="36" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="59" spans="5:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="5:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E59" s="66"/>
       <c r="F59" s="36" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="60" spans="5:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="61" spans="5:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="5:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="61" spans="5:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F61" s="36" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="62" spans="5:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="62" spans="5:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F62" s="36" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="63" spans="5:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="63" spans="5:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F63" s="36" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="64" spans="5:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="65" spans="4:35" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="64" spans="5:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="65" spans="4:35" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E65" s="66"/>
       <c r="F65" s="36" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="66" spans="4:35" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="66" spans="4:35" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E66" s="66"/>
       <c r="F66" s="36" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="67" spans="4:35" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="67" spans="4:35" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F67" s="36" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="68" spans="4:35" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="68" spans="4:35" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F68" s="36" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="69" spans="4:35" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F69" s="36" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="70" spans="4:35" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="71" spans="4:35" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F71" s="132" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="72" spans="4:35" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="73" spans="4:35" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F73" s="36" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="69" spans="4:35" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F69" s="36" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="70" spans="4:35" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="71" spans="4:35" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F71" s="110" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="72" spans="4:35" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="73" spans="4:35" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F73" s="36" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="74" spans="4:35" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="75" spans="4:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="74" spans="4:35" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="75" spans="4:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D75" s="28" t="str">
         <f>$C$7&amp;"5."</f>
         <v>3.1.5.</v>
@@ -6121,7 +6130,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="76" spans="4:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="76" spans="4:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D76" s="28"/>
       <c r="E76" s="28" t="str">
         <f>D75&amp;"1."</f>
@@ -6132,7 +6141,7 @@
         <v>二重サブミット防止機能概要</v>
       </c>
     </row>
-    <row r="77" spans="4:35" s="41" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="77" spans="4:35" s="41" customFormat="1" ht="11" x14ac:dyDescent="0.2">
       <c r="D77" s="29"/>
       <c r="F77" s="41" t="s">
         <v>195</v>
@@ -6152,7 +6161,7 @@
       <c r="AH77" s="29"/>
       <c r="AI77" s="29"/>
     </row>
-    <row r="78" spans="4:35" s="41" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="78" spans="4:35" s="41" customFormat="1" ht="11" x14ac:dyDescent="0.2">
       <c r="D78" s="29"/>
       <c r="F78" s="41" t="s">
         <v>196</v>
@@ -6172,7 +6181,7 @@
       <c r="AH78" s="29"/>
       <c r="AI78" s="29"/>
     </row>
-    <row r="79" spans="4:35" s="41" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
+    <row r="79" spans="4:35" s="41" customFormat="1" ht="11" x14ac:dyDescent="0.2">
       <c r="D79" s="29"/>
       <c r="F79" s="41" t="s">
         <v>197</v>
@@ -6192,8 +6201,8 @@
       <c r="AH79" s="29"/>
       <c r="AI79" s="29"/>
     </row>
-    <row r="80" spans="4:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="81" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="80" spans="4:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="81" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E81" s="28" t="str">
         <f>D75&amp;"2."</f>
         <v>3.1.5.2.</v>
@@ -6203,12 +6212,12 @@
         <v>二重サブミット防止方法</v>
       </c>
     </row>
-    <row r="82" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="82" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F82" s="36" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="83" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="83" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F83" s="16" t="s">
         <v>18</v>
       </c>
@@ -6243,7 +6252,7 @@
       <c r="AG83" s="17"/>
       <c r="AH83" s="18"/>
     </row>
-    <row r="84" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="84" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C84" s="29"/>
       <c r="D84" s="29"/>
       <c r="E84" s="29"/>
@@ -6281,7 +6290,7 @@
       <c r="AG84" s="70"/>
       <c r="AH84" s="94"/>
     </row>
-    <row r="85" spans="3:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="85" spans="3:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C85" s="29"/>
       <c r="D85" s="29"/>
       <c r="E85" s="29"/>
@@ -6317,7 +6326,7 @@
       <c r="AG85" s="70"/>
       <c r="AH85" s="94"/>
     </row>
-    <row r="86" spans="3:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="86" spans="3:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C86" s="29"/>
       <c r="D86" s="29"/>
       <c r="E86" s="29"/>
@@ -6353,7 +6362,7 @@
       <c r="AG86" s="70"/>
       <c r="AH86" s="94"/>
     </row>
-    <row r="87" spans="3:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="87" spans="3:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C87" s="29"/>
       <c r="D87" s="29"/>
       <c r="E87" s="29"/>
@@ -6362,7 +6371,7 @@
       <c r="H87" s="26"/>
       <c r="I87" s="26"/>
       <c r="J87" s="92" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="K87" s="26"/>
       <c r="L87" s="26"/>
@@ -6389,7 +6398,7 @@
       <c r="AG87" s="70"/>
       <c r="AH87" s="94"/>
     </row>
-    <row r="88" spans="3:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="88" spans="3:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C88" s="29"/>
       <c r="D88" s="29"/>
       <c r="E88" s="29"/>
@@ -6398,7 +6407,7 @@
       <c r="H88" s="26"/>
       <c r="I88" s="26"/>
       <c r="J88" s="75" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="K88" s="26"/>
       <c r="L88" s="26"/>
@@ -6425,7 +6434,7 @@
       <c r="AG88" s="70"/>
       <c r="AH88" s="94"/>
     </row>
-    <row r="89" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="89" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C89" s="29"/>
       <c r="D89" s="29"/>
       <c r="E89" s="29"/>
@@ -6463,7 +6472,7 @@
       <c r="AG89" s="98"/>
       <c r="AH89" s="100"/>
     </row>
-    <row r="90" spans="3:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="90" spans="3:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C90" s="29"/>
       <c r="D90" s="29"/>
       <c r="E90" s="29"/>
@@ -6499,7 +6508,7 @@
       <c r="AG90" s="70"/>
       <c r="AH90" s="94"/>
     </row>
-    <row r="91" spans="3:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="91" spans="3:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C91" s="29"/>
       <c r="D91" s="29"/>
       <c r="E91" s="29"/>
@@ -6535,7 +6544,7 @@
       <c r="AG91" s="70"/>
       <c r="AH91" s="94"/>
     </row>
-    <row r="92" spans="3:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="92" spans="3:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C92" s="29"/>
       <c r="D92" s="29"/>
       <c r="E92" s="29"/>
@@ -6571,7 +6580,7 @@
       <c r="AG92" s="101"/>
       <c r="AH92" s="102"/>
     </row>
-    <row r="93" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="93" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C93" s="29"/>
       <c r="D93" s="29"/>
       <c r="E93" s="29"/>
@@ -6605,7 +6614,7 @@
       <c r="AG93" s="19"/>
       <c r="AH93" s="19"/>
     </row>
-    <row r="94" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="94" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C94" s="29"/>
       <c r="D94" s="29"/>
       <c r="E94" s="24" t="str">
@@ -6637,7 +6646,7 @@
       <c r="Z94" s="29"/>
       <c r="AA94" s="29"/>
     </row>
-    <row r="95" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="95" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C95" s="29"/>
       <c r="D95" s="29"/>
       <c r="E95" s="29"/>
@@ -6666,7 +6675,7 @@
       <c r="Z95" s="29"/>
       <c r="AA95" s="29"/>
     </row>
-    <row r="96" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="96" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C96" s="29"/>
       <c r="D96" s="29"/>
       <c r="E96" s="29"/>
@@ -6695,7 +6704,7 @@
       <c r="Z96" s="29"/>
       <c r="AA96" s="29"/>
     </row>
-    <row r="97" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="97" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C97" s="29"/>
       <c r="D97" s="29"/>
       <c r="E97" s="29"/>
@@ -6722,7 +6731,7 @@
       <c r="Z97" s="29"/>
       <c r="AA97" s="29"/>
     </row>
-    <row r="98" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="98" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C98" s="29"/>
       <c r="D98" s="29"/>
       <c r="E98" s="29"/>
@@ -6751,8 +6760,8 @@
       <c r="Z98" s="29"/>
       <c r="AA98" s="29"/>
     </row>
-    <row r="99" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="100" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="99" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="100" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D100" s="28" t="str">
         <f>$C$7&amp;"6."</f>
         <v>3.1.6.</v>
@@ -6761,7 +6770,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="101" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="101" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D101" s="28"/>
       <c r="E101" s="28" t="str">
         <f>D100&amp;"1."</f>
@@ -6772,13 +6781,13 @@
         <v>データの保持機能概要</v>
       </c>
     </row>
-    <row r="102" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="102" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F102" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="103" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="104" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="103" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="104" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E104" s="28" t="str">
         <f>D100&amp;"2."</f>
         <v>3.1.6.2.</v>
@@ -6788,12 +6797,12 @@
         <v>データの保持方法</v>
       </c>
     </row>
-    <row r="105" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="105" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F105" s="4" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="106" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="106" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F106" s="16" t="str">
         <f>F104</f>
         <v>データの保持方法</v>
@@ -6829,7 +6838,7 @@
       <c r="AG106" s="17"/>
       <c r="AH106" s="18"/>
     </row>
-    <row r="107" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="107" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F107" s="69" t="s">
         <v>31</v>
       </c>
@@ -6864,7 +6873,7 @@
       <c r="AG107" s="70"/>
       <c r="AH107" s="94"/>
     </row>
-    <row r="108" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="108" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F108" s="103"/>
       <c r="G108" s="101"/>
       <c r="H108" s="101"/>
@@ -6897,7 +6906,7 @@
       <c r="AG108" s="101"/>
       <c r="AH108" s="102"/>
     </row>
-    <row r="109" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="109" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F109" s="69" t="s">
         <v>32</v>
       </c>
@@ -6932,7 +6941,7 @@
       <c r="AG109" s="70"/>
       <c r="AH109" s="94"/>
     </row>
-    <row r="110" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="110" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F110" s="81"/>
       <c r="G110" s="101"/>
       <c r="H110" s="101"/>
@@ -6965,7 +6974,7 @@
       <c r="AG110" s="101"/>
       <c r="AH110" s="102"/>
     </row>
-    <row r="111" spans="3:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="111" spans="3:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F111" s="70"/>
       <c r="G111" s="70"/>
       <c r="H111" s="70"/>
@@ -6996,7 +7005,7 @@
       <c r="AG111" s="70"/>
       <c r="AH111" s="70"/>
     </row>
-    <row r="112" spans="3:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="112" spans="3:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F112" s="70" t="s">
         <v>253</v>
       </c>
@@ -7029,7 +7038,7 @@
       <c r="AG112" s="70"/>
       <c r="AH112" s="70"/>
     </row>
-    <row r="113" spans="5:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="113" spans="5:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F113" s="70"/>
       <c r="G113" s="70"/>
       <c r="H113" s="70"/>
@@ -7060,7 +7069,7 @@
       <c r="AG113" s="70"/>
       <c r="AH113" s="70"/>
     </row>
-    <row r="114" spans="5:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="114" spans="5:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F114" s="52" t="s">
         <v>25</v>
       </c>
@@ -7095,7 +7104,7 @@
       <c r="AG114" s="54"/>
       <c r="AH114" s="70"/>
     </row>
-    <row r="115" spans="5:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="115" spans="5:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F115" s="69" t="s">
         <v>26</v>
       </c>
@@ -7130,7 +7139,7 @@
       <c r="AG115" s="100"/>
       <c r="AH115" s="70"/>
     </row>
-    <row r="116" spans="5:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="116" spans="5:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F116" s="103"/>
       <c r="G116" s="70"/>
       <c r="H116" s="70"/>
@@ -7163,7 +7172,7 @@
       <c r="AG116" s="94"/>
       <c r="AH116" s="70"/>
     </row>
-    <row r="117" spans="5:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="117" spans="5:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F117" s="81"/>
       <c r="G117" s="101"/>
       <c r="H117" s="101"/>
@@ -7196,7 +7205,7 @@
       <c r="AG117" s="102"/>
       <c r="AH117" s="70"/>
     </row>
-    <row r="118" spans="5:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="5:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F118" s="103" t="s">
         <v>27</v>
       </c>
@@ -7231,7 +7240,7 @@
       <c r="AG118" s="94"/>
       <c r="AH118" s="70"/>
     </row>
-    <row r="119" spans="5:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="119" spans="5:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F119" s="103"/>
       <c r="G119" s="70"/>
       <c r="H119" s="70"/>
@@ -7264,7 +7273,7 @@
       <c r="AG119" s="94"/>
       <c r="AH119" s="70"/>
     </row>
-    <row r="120" spans="5:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="120" spans="5:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F120" s="69" t="s">
         <v>28</v>
       </c>
@@ -7299,7 +7308,7 @@
       <c r="AG120" s="100"/>
       <c r="AH120" s="70"/>
     </row>
-    <row r="121" spans="5:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="121" spans="5:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F121" s="103" t="s">
         <v>29</v>
       </c>
@@ -7334,7 +7343,7 @@
       <c r="AG121" s="94"/>
       <c r="AH121" s="70"/>
     </row>
-    <row r="122" spans="5:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="122" spans="5:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F122" s="81"/>
       <c r="G122" s="101"/>
       <c r="H122" s="101"/>
@@ -7367,7 +7376,7 @@
       <c r="AG122" s="102"/>
       <c r="AH122" s="70"/>
     </row>
-    <row r="123" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="123" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F123" s="19"/>
       <c r="G123" s="19"/>
       <c r="H123" s="19"/>
@@ -7398,7 +7407,7 @@
       <c r="AG123" s="19"/>
       <c r="AH123" s="19"/>
     </row>
-    <row r="124" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="124" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E124" s="28" t="str">
         <f>D100&amp;"3."</f>
         <v>3.1.6.3.</v>
@@ -7407,7 +7416,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="125" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="125" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F125" s="24" t="s">
         <v>53</v>
       </c>
@@ -7415,41 +7424,41 @@
         <v>261</v>
       </c>
     </row>
-    <row r="126" spans="5:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="126" spans="5:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F126" s="24"/>
       <c r="G126" s="41" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="127" spans="5:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="127" spans="5:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F127" s="24"/>
       <c r="G127" s="41" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="128" spans="5:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="128" spans="5:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F128" s="24"/>
     </row>
-    <row r="129" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="129" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F129" s="24"/>
       <c r="G129" s="41" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="130" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="130" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F130" s="24"/>
       <c r="G130" s="41" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="131" spans="2:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="131" spans="2:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B131" s="36"/>
       <c r="C131" s="36"/>
       <c r="D131" s="36"/>
       <c r="E131" s="36"/>
       <c r="AA131" s="41"/>
     </row>
-    <row r="132" spans="2:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="132" spans="2:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B132" s="36"/>
       <c r="C132" s="36"/>
       <c r="D132" s="36"/>
@@ -7489,7 +7498,7 @@
       <c r="AG132" s="17"/>
       <c r="AH132" s="18"/>
     </row>
-    <row r="133" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="133" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B133" s="36"/>
       <c r="C133" s="36"/>
       <c r="D133" s="36"/>
@@ -7530,7 +7539,7 @@
       <c r="AH133" s="100"/>
       <c r="AI133" s="44"/>
     </row>
-    <row r="134" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="134" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B134" s="36"/>
       <c r="C134" s="36"/>
       <c r="D134" s="36"/>
@@ -7566,7 +7575,7 @@
       <c r="AG134" s="70"/>
       <c r="AH134" s="94"/>
     </row>
-    <row r="135" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="135" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B135" s="36"/>
       <c r="C135" s="36"/>
       <c r="D135" s="36"/>
@@ -7602,7 +7611,7 @@
       <c r="AG135" s="101"/>
       <c r="AH135" s="102"/>
     </row>
-    <row r="136" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="136" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G136" s="103" t="s">
         <v>27</v>
       </c>
@@ -7638,7 +7647,7 @@
       <c r="AG136" s="70"/>
       <c r="AH136" s="94"/>
     </row>
-    <row r="137" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="137" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G137" s="81"/>
       <c r="H137" s="101"/>
       <c r="I137" s="101"/>
@@ -7668,7 +7677,7 @@
       <c r="AG137" s="101"/>
       <c r="AH137" s="102"/>
     </row>
-    <row r="138" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="138" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G138" s="103" t="s">
         <v>28</v>
       </c>
@@ -7704,7 +7713,7 @@
       <c r="AG138" s="70"/>
       <c r="AH138" s="94"/>
     </row>
-    <row r="139" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="139" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G139" s="81" t="s">
         <v>29</v>
       </c>
@@ -7736,8 +7745,8 @@
       <c r="AG139" s="101"/>
       <c r="AH139" s="102"/>
     </row>
-    <row r="140" spans="2:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="141" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="140" spans="2:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="141" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F141" s="24" t="s">
         <v>52</v>
       </c>
@@ -7745,7 +7754,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="142" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="142" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B142" s="36"/>
       <c r="C142" s="36"/>
       <c r="D142" s="36"/>
@@ -7754,13 +7763,13 @@
         <v>265</v>
       </c>
     </row>
-    <row r="143" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="143" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B143" s="36"/>
       <c r="C143" s="36"/>
       <c r="D143" s="36"/>
       <c r="E143" s="36"/>
     </row>
-    <row r="144" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="144" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B144" s="36"/>
       <c r="C144" s="36"/>
       <c r="D144" s="36"/>
@@ -7800,7 +7809,7 @@
       <c r="AG144" s="53"/>
       <c r="AH144" s="54"/>
     </row>
-    <row r="145" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="145" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B145" s="36"/>
       <c r="C145" s="36"/>
       <c r="D145" s="36"/>
@@ -7841,7 +7850,7 @@
       <c r="AH145" s="100"/>
       <c r="AI145" s="44"/>
     </row>
-    <row r="146" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="146" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B146" s="36"/>
       <c r="C146" s="36"/>
       <c r="D146" s="36"/>
@@ -7875,8 +7884,8 @@
       <c r="AG146" s="101"/>
       <c r="AH146" s="102"/>
     </row>
-    <row r="147" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="148" spans="2:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="147" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="148" spans="2:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C148" s="29"/>
       <c r="D148" s="24" t="str">
         <f>$C$7&amp;"7."</f>
@@ -7909,7 +7918,7 @@
       <c r="AA148" s="29"/>
       <c r="AB148" s="29"/>
     </row>
-    <row r="149" spans="2:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="149" spans="2:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C149" s="29"/>
       <c r="D149" s="24"/>
       <c r="E149" s="24" t="str">
@@ -7943,7 +7952,7 @@
       <c r="AA149" s="29"/>
       <c r="AB149" s="29"/>
     </row>
-    <row r="150" spans="2:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="150" spans="2:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C150" s="29"/>
       <c r="D150" s="29"/>
       <c r="E150" s="29"/>
@@ -7973,7 +7982,7 @@
       <c r="AA150" s="29"/>
       <c r="AB150" s="29"/>
     </row>
-    <row r="151" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="151" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C151" s="29"/>
       <c r="D151" s="29"/>
       <c r="E151" s="29"/>
@@ -8003,7 +8012,7 @@
       <c r="AA151" s="29"/>
       <c r="AB151" s="29"/>
     </row>
-    <row r="152" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="152" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C152" s="29"/>
       <c r="D152" s="29"/>
       <c r="E152" s="29"/>
@@ -8035,7 +8044,7 @@
       <c r="AA152" s="29"/>
       <c r="AB152" s="29"/>
     </row>
-    <row r="153" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="153" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C153" s="29"/>
       <c r="D153" s="29"/>
       <c r="E153" s="29"/>
@@ -8067,7 +8076,7 @@
       <c r="AA153" s="29"/>
       <c r="AB153" s="29"/>
     </row>
-    <row r="154" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="154" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C154" s="29"/>
       <c r="D154" s="29"/>
       <c r="E154" s="29"/>
@@ -8099,7 +8108,7 @@
       <c r="AA154" s="29"/>
       <c r="AB154" s="29"/>
     </row>
-    <row r="155" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="155" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C155" s="29"/>
       <c r="D155" s="29"/>
       <c r="E155" s="29"/>
@@ -8131,7 +8140,7 @@
       <c r="AA155" s="29"/>
       <c r="AB155" s="29"/>
     </row>
-    <row r="156" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="156" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C156" s="29"/>
       <c r="D156" s="29"/>
       <c r="E156" s="29"/>
@@ -8163,7 +8172,7 @@
       <c r="AA156" s="29"/>
       <c r="AB156" s="29"/>
     </row>
-    <row r="157" spans="2:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="157" spans="2:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C157" s="29"/>
       <c r="D157" s="29"/>
       <c r="E157" s="29"/>
@@ -8191,7 +8200,7 @@
       <c r="AA157" s="29"/>
       <c r="AB157" s="29"/>
     </row>
-    <row r="158" spans="2:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="158" spans="2:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C158" s="29"/>
       <c r="D158" s="29"/>
       <c r="E158" s="24" t="str">
@@ -8224,7 +8233,7 @@
       <c r="AA158" s="29"/>
       <c r="AB158" s="29"/>
     </row>
-    <row r="159" spans="2:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="159" spans="2:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C159" s="29"/>
       <c r="D159" s="29"/>
       <c r="E159" s="29"/>
@@ -8254,7 +8263,7 @@
       <c r="AA159" s="29"/>
       <c r="AB159" s="29"/>
     </row>
-    <row r="160" spans="2:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="160" spans="2:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C160" s="29"/>
       <c r="D160" s="29"/>
       <c r="E160" s="29"/>
@@ -8282,7 +8291,7 @@
       <c r="AA160" s="29"/>
       <c r="AB160" s="29"/>
     </row>
-    <row r="161" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="161" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C161" s="29"/>
       <c r="D161" s="29"/>
       <c r="E161" s="29"/>
@@ -8320,7 +8329,7 @@
       <c r="AG161" s="53"/>
       <c r="AH161" s="54"/>
     </row>
-    <row r="162" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="162" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C162" s="29"/>
       <c r="D162" s="29"/>
       <c r="E162" s="29"/>
@@ -8358,7 +8367,7 @@
       <c r="AG162" s="98"/>
       <c r="AH162" s="100"/>
     </row>
-    <row r="163" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="163" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C163" s="29"/>
       <c r="D163" s="29"/>
       <c r="E163" s="29"/>
@@ -8396,7 +8405,7 @@
       <c r="AG163" s="98"/>
       <c r="AH163" s="100"/>
     </row>
-    <row r="164" spans="1:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="164" spans="1:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C164" s="29"/>
       <c r="D164" s="29"/>
       <c r="E164" s="29"/>
@@ -8432,7 +8441,7 @@
       <c r="AG164" s="101"/>
       <c r="AH164" s="102"/>
     </row>
-    <row r="165" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="165" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C165" s="29"/>
       <c r="D165" s="29"/>
       <c r="E165" s="29"/>
@@ -8460,7 +8469,7 @@
       <c r="AA165" s="29"/>
       <c r="AB165" s="29"/>
     </row>
-    <row r="166" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="166" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C166" s="29"/>
       <c r="D166" s="29"/>
       <c r="E166" s="24" t="str">
@@ -8493,7 +8502,7 @@
       <c r="AA166" s="29"/>
       <c r="AB166" s="29"/>
     </row>
-    <row r="167" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="167" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C167" s="29"/>
       <c r="D167" s="29"/>
       <c r="E167" s="77"/>
@@ -8525,13 +8534,13 @@
       <c r="AA167" s="29"/>
       <c r="AB167" s="29"/>
     </row>
-    <row r="168" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="168" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C168" s="29"/>
       <c r="D168" s="29"/>
       <c r="E168" s="77"/>
       <c r="F168" s="24"/>
       <c r="G168" s="29" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="H168" s="29"/>
       <c r="I168" s="29"/>
@@ -8555,13 +8564,13 @@
       <c r="AA168" s="29"/>
       <c r="AB168" s="29"/>
     </row>
-    <row r="169" spans="1:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="169" spans="1:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C169" s="29"/>
       <c r="D169" s="29"/>
       <c r="E169" s="77"/>
       <c r="F169" s="24"/>
       <c r="G169" s="29" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="H169" s="29"/>
       <c r="I169" s="29"/>
@@ -8585,7 +8594,7 @@
       <c r="AA169" s="29"/>
       <c r="AB169" s="29"/>
     </row>
-    <row r="170" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="170" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C170" s="29"/>
       <c r="D170" s="29"/>
       <c r="E170" s="77"/>
@@ -8615,7 +8624,7 @@
       <c r="AA170" s="29"/>
       <c r="AB170" s="29"/>
     </row>
-    <row r="171" spans="1:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="171" spans="1:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C171" s="29"/>
       <c r="D171" s="29"/>
       <c r="E171" s="77"/>
@@ -8645,7 +8654,7 @@
       <c r="AA171" s="29"/>
       <c r="AB171" s="29"/>
     </row>
-    <row r="172" spans="1:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="172" spans="1:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C172" s="29"/>
       <c r="D172" s="29"/>
       <c r="E172" s="77"/>
@@ -8673,7 +8682,7 @@
       <c r="AA172" s="29"/>
       <c r="AB172" s="29"/>
     </row>
-    <row r="173" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="173" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="41"/>
       <c r="C173" s="29"/>
       <c r="D173" s="29"/>
@@ -8707,7 +8716,7 @@
       <c r="AA173" s="29"/>
       <c r="AB173" s="29"/>
     </row>
-    <row r="174" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="174" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="41"/>
       <c r="C174" s="29"/>
       <c r="D174" s="29"/>
@@ -8749,7 +8758,7 @@
       <c r="AG174" s="17"/>
       <c r="AH174" s="18"/>
     </row>
-    <row r="175" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="175" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="41"/>
       <c r="C175" s="29"/>
       <c r="D175" s="29"/>
@@ -8791,7 +8800,7 @@
       <c r="AG175" s="19"/>
       <c r="AH175" s="20"/>
     </row>
-    <row r="176" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="176" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="41"/>
       <c r="C176" s="29"/>
       <c r="D176" s="29"/>
@@ -8833,7 +8842,7 @@
       <c r="AG176" s="59"/>
       <c r="AH176" s="60"/>
     </row>
-    <row r="177" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="177" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="41"/>
       <c r="C177" s="29"/>
       <c r="D177" s="29"/>
@@ -8868,7 +8877,7 @@
       <c r="AG177" s="19"/>
       <c r="AH177" s="19"/>
     </row>
-    <row r="178" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="178" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C178" s="29"/>
       <c r="D178" s="29"/>
       <c r="E178" s="74"/>
@@ -8901,7 +8910,7 @@
       <c r="AA178" s="29"/>
       <c r="AB178" s="29"/>
     </row>
-    <row r="179" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="179" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C179" s="29"/>
       <c r="D179" s="29"/>
       <c r="E179" s="74"/>
@@ -8941,7 +8950,7 @@
       <c r="AG179" s="53"/>
       <c r="AH179" s="54"/>
     </row>
-    <row r="180" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="180" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C180" s="29"/>
       <c r="D180" s="29"/>
       <c r="E180" s="74"/>
@@ -8982,7 +8991,7 @@
       <c r="AG180" s="21"/>
       <c r="AH180" s="22"/>
     </row>
-    <row r="181" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="181" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C181" s="29"/>
       <c r="D181" s="29"/>
       <c r="E181" s="74"/>
@@ -9010,7 +9019,7 @@
       <c r="AA181" s="29"/>
       <c r="AB181" s="29"/>
     </row>
-    <row r="182" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="182" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C182" s="29"/>
       <c r="D182" s="29"/>
       <c r="E182" s="74"/>
@@ -9043,7 +9052,7 @@
       <c r="AA182" s="29"/>
       <c r="AB182" s="29"/>
     </row>
-    <row r="183" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="183" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C183" s="29"/>
       <c r="D183" s="29"/>
       <c r="E183" s="74"/>
@@ -9083,7 +9092,7 @@
       <c r="AG183" s="17"/>
       <c r="AH183" s="18"/>
     </row>
-    <row r="184" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="184" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C184" s="29"/>
       <c r="D184" s="29"/>
       <c r="E184" s="26"/>
@@ -9124,7 +9133,7 @@
       <c r="AG184" s="49"/>
       <c r="AH184" s="50"/>
     </row>
-    <row r="185" spans="1:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="185" spans="1:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C185" s="29"/>
       <c r="D185" s="29"/>
       <c r="E185" s="74"/>
@@ -9162,7 +9171,7 @@
       <c r="AG185" s="44"/>
       <c r="AH185" s="45"/>
     </row>
-    <row r="186" spans="1:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="186" spans="1:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C186" s="29"/>
       <c r="D186" s="29"/>
       <c r="E186" s="74"/>
@@ -9198,7 +9207,7 @@
       <c r="AG186" s="47"/>
       <c r="AH186" s="51"/>
     </row>
-    <row r="187" spans="1:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="187" spans="1:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C187" s="29"/>
       <c r="D187" s="29"/>
       <c r="E187" s="74"/>
@@ -9232,7 +9241,7 @@
       <c r="AG187" s="44"/>
       <c r="AH187" s="44"/>
     </row>
-    <row r="188" spans="1:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="188" spans="1:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C188" s="29"/>
       <c r="D188" s="29"/>
       <c r="E188" s="74"/>
@@ -9271,7 +9280,7 @@
       <c r="AG188" s="44"/>
       <c r="AH188" s="44"/>
     </row>
-    <row r="189" spans="1:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="189" spans="1:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C189" s="29"/>
       <c r="D189" s="29"/>
       <c r="E189" s="74"/>
@@ -9307,7 +9316,7 @@
       <c r="AG189" s="44"/>
       <c r="AH189" s="44"/>
     </row>
-    <row r="190" spans="1:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="190" spans="1:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C190" s="29"/>
       <c r="D190" s="29"/>
       <c r="E190" s="74"/>
@@ -9341,7 +9350,7 @@
       <c r="AG190" s="44"/>
       <c r="AH190" s="44"/>
     </row>
-    <row r="191" spans="1:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="191" spans="1:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C191" s="29"/>
       <c r="D191" s="29"/>
       <c r="E191" s="74"/>
@@ -9380,13 +9389,13 @@
       <c r="AG191" s="44"/>
       <c r="AH191" s="44"/>
     </row>
-    <row r="192" spans="1:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="192" spans="1:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C192" s="29"/>
       <c r="D192" s="29"/>
       <c r="E192" s="74"/>
       <c r="F192" s="24"/>
       <c r="G192" s="55" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="H192" s="55"/>
       <c r="I192" s="55"/>
@@ -9416,13 +9425,13 @@
       <c r="AG192" s="44"/>
       <c r="AH192" s="44"/>
     </row>
-    <row r="193" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="193" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C193" s="29"/>
       <c r="D193" s="29"/>
       <c r="E193" s="74"/>
       <c r="F193" s="24"/>
       <c r="G193" s="55" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="H193" s="55"/>
       <c r="I193" s="55"/>
@@ -9452,13 +9461,13 @@
       <c r="AG193" s="44"/>
       <c r="AH193" s="44"/>
     </row>
-    <row r="194" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="194" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C194" s="29"/>
       <c r="D194" s="29"/>
       <c r="E194" s="74"/>
       <c r="F194" s="24"/>
       <c r="G194" s="55" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="H194" s="55"/>
       <c r="I194" s="55"/>
@@ -9488,13 +9497,13 @@
       <c r="AG194" s="44"/>
       <c r="AH194" s="44"/>
     </row>
-    <row r="195" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="195" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C195" s="29"/>
       <c r="D195" s="29"/>
       <c r="E195" s="74"/>
       <c r="F195" s="24"/>
       <c r="G195" s="55" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="H195" s="55"/>
       <c r="I195" s="55"/>
@@ -9524,7 +9533,7 @@
       <c r="AG195" s="44"/>
       <c r="AH195" s="44"/>
     </row>
-    <row r="196" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="196" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C196" s="29"/>
       <c r="D196" s="29"/>
       <c r="E196" s="29"/>
@@ -9552,7 +9561,7 @@
       <c r="AA196" s="29"/>
       <c r="AB196" s="29"/>
     </row>
-    <row r="197" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="197" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="29"/>
       <c r="B197" s="29"/>
       <c r="C197" s="29"/>
@@ -9594,7 +9603,7 @@
       <c r="AH197" s="29"/>
       <c r="AI197" s="29"/>
     </row>
-    <row r="198" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="198" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C198" s="42"/>
       <c r="D198" s="42"/>
       <c r="E198" s="63" t="str">
@@ -9602,149 +9611,149 @@
         <v>3.1.8.1.</v>
       </c>
       <c r="F198" s="41" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="199" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F199" s="41" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="200" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="201" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F201" s="63" t="s">
         <v>303</v>
       </c>
-    </row>
-    <row r="199" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F199" s="41" t="s">
+      <c r="G201" s="41" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="200" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="201" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F201" s="63" t="s">
+    <row r="202" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G202" s="41" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="203" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G203" s="41" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="204" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G204" s="41" t="s">
         <v>305</v>
       </c>
-      <c r="G201" s="41" t="s">
+    </row>
+    <row r="205" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="206" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F206" s="63" t="s">
         <v>306</v>
       </c>
-    </row>
-    <row r="202" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="G202" s="41" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="203" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="G203" s="41" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="204" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="G204" s="41" t="s">
+      <c r="G206" s="41" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="205" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="206" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F206" s="63" t="s">
+    <row r="207" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G207" s="41" t="s">
         <v>308</v>
       </c>
-      <c r="G206" s="41" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="207" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="G207" s="41" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="208" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="209" spans="5:7" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="208" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="209" spans="5:7" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E209" s="63" t="str">
         <f>$D$197&amp;"2."</f>
         <v>3.1.8.2.</v>
       </c>
       <c r="F209" s="41" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="210" spans="5:7" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="211" spans="5:7" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="210" spans="5:7" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="211" spans="5:7" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F211" s="63" t="str">
         <f>$E$209&amp;"1."</f>
         <v>3.1.8.2.1.</v>
       </c>
       <c r="G211" s="41" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="212" spans="5:7" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G212" s="41" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="213" spans="5:7" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G213" s="41" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="212" spans="5:7" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="G212" s="41" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="213" spans="5:7" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="G213" s="41" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="214" spans="5:7" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="214" spans="5:7" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G214" s="41" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="215" spans="5:7" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="215" spans="5:7" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G215" s="41" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="216" spans="5:7" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="217" spans="5:7" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="216" spans="5:7" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="217" spans="5:7" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F217" s="63" t="str">
         <f>$E$209&amp;"2."</f>
         <v>3.1.8.2.2.</v>
       </c>
       <c r="G217" s="41" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="218" spans="5:7" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G218" s="41" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="219" spans="5:7" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G219" s="41" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="218" spans="5:7" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="G218" s="41" t="s">
+    <row r="220" spans="5:7" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G220" s="41" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="219" spans="5:7" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="G219" s="41" t="s">
+    <row r="221" spans="5:7" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G221" s="41" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="220" spans="5:7" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="G220" s="41" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="221" spans="5:7" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="G221" s="41" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="222" spans="5:7" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="223" spans="5:7" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="222" spans="5:7" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="223" spans="5:7" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F223" s="63" t="str">
         <f>$E$209&amp;"3."</f>
         <v>3.1.8.2.3.</v>
       </c>
       <c r="G223" s="41" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="224" spans="5:7" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G224" s="41" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="225" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G225" s="41" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="224" spans="5:7" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="G224" s="41" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="225" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="G225" s="41" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="226" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="226" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="G226" s="41" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="227" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="228" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="227" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="228" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="29"/>
       <c r="B228" s="29"/>
       <c r="C228" s="29"/>
@@ -9786,14 +9795,14 @@
       <c r="AH228" s="29"/>
       <c r="AI228" s="29"/>
     </row>
-    <row r="229" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="229" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="29"/>
       <c r="B229" s="29"/>
       <c r="C229" s="29"/>
       <c r="D229" s="29"/>
       <c r="E229" s="24"/>
       <c r="F229" s="29" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="G229" s="29"/>
       <c r="H229" s="29"/>
@@ -9825,7 +9834,7 @@
       <c r="AH229" s="29"/>
       <c r="AI229" s="29"/>
     </row>
-    <row r="230" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="230" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="29"/>
       <c r="B230" s="29"/>
       <c r="C230" s="29"/>
@@ -9862,7 +9871,7 @@
       <c r="AH230" s="29"/>
       <c r="AI230" s="29"/>
     </row>
-    <row r="231" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="231" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="29"/>
       <c r="B231" s="29"/>
       <c r="C231" s="29"/>
@@ -9903,7 +9912,7 @@
       <c r="AH231" s="29"/>
       <c r="AI231" s="29"/>
     </row>
-    <row r="232" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="232" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A232" s="29"/>
       <c r="B232" s="29"/>
       <c r="C232" s="29"/>
@@ -9942,7 +9951,7 @@
       <c r="AH232" s="29"/>
       <c r="AI232" s="29"/>
     </row>
-    <row r="233" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="233" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A233" s="29"/>
       <c r="B233" s="29"/>
       <c r="C233" s="29"/>
@@ -9985,7 +9994,7 @@
       <c r="AH233" s="37"/>
       <c r="AI233" s="29"/>
     </row>
-    <row r="234" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="234" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234" s="29"/>
       <c r="B234" s="29"/>
       <c r="C234" s="29"/>
@@ -10028,7 +10037,7 @@
       <c r="AH234" s="71"/>
       <c r="AI234" s="29"/>
     </row>
-    <row r="235" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="235" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A235" s="29"/>
       <c r="B235" s="29"/>
       <c r="C235" s="29"/>
@@ -10069,7 +10078,7 @@
       <c r="AH235" s="71"/>
       <c r="AI235" s="29"/>
     </row>
-    <row r="236" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="236" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A236" s="29"/>
       <c r="B236" s="29"/>
       <c r="C236" s="29"/>
@@ -10108,7 +10117,7 @@
       <c r="AH236" s="71"/>
       <c r="AI236" s="29"/>
     </row>
-    <row r="237" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="237" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A237" s="29"/>
       <c r="B237" s="29"/>
       <c r="C237" s="29"/>
@@ -10147,7 +10156,7 @@
       <c r="AH237" s="90"/>
       <c r="AI237" s="29"/>
     </row>
-    <row r="238" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="238" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A238" s="29"/>
       <c r="B238" s="29"/>
       <c r="C238" s="29"/>
@@ -10190,7 +10199,7 @@
       <c r="AH238" s="71"/>
       <c r="AI238" s="29"/>
     </row>
-    <row r="239" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="239" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A239" s="29"/>
       <c r="B239" s="29"/>
       <c r="C239" s="29"/>
@@ -10231,7 +10240,7 @@
       <c r="AH239" s="71"/>
       <c r="AI239" s="29"/>
     </row>
-    <row r="240" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="240" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A240" s="29"/>
       <c r="B240" s="29"/>
       <c r="C240" s="29"/>
@@ -10270,7 +10279,7 @@
       <c r="AH240" s="71"/>
       <c r="AI240" s="29"/>
     </row>
-    <row r="241" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="241" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A241" s="29"/>
       <c r="B241" s="29"/>
       <c r="C241" s="29"/>
@@ -10307,7 +10316,7 @@
       <c r="AH241" s="90"/>
       <c r="AI241" s="29"/>
     </row>
-    <row r="242" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="242" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A242" s="29"/>
       <c r="B242" s="29"/>
       <c r="C242" s="29"/>
@@ -10350,7 +10359,7 @@
       <c r="AH242" s="71"/>
       <c r="AI242" s="29"/>
     </row>
-    <row r="243" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="243" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A243" s="29"/>
       <c r="B243" s="29"/>
       <c r="C243" s="29"/>
@@ -10391,7 +10400,7 @@
       <c r="AH243" s="71"/>
       <c r="AI243" s="29"/>
     </row>
-    <row r="244" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="244" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A244" s="29"/>
       <c r="B244" s="29"/>
       <c r="C244" s="29"/>
@@ -10430,7 +10439,7 @@
       <c r="AH244" s="71"/>
       <c r="AI244" s="29"/>
     </row>
-    <row r="245" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="245" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245" s="29"/>
       <c r="B245" s="29"/>
       <c r="C245" s="29"/>
@@ -10469,7 +10478,7 @@
       <c r="AH245" s="71"/>
       <c r="AI245" s="29"/>
     </row>
-    <row r="246" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="246" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" s="29"/>
       <c r="B246" s="29"/>
       <c r="C246" s="29"/>
@@ -10506,7 +10515,7 @@
       <c r="AH246" s="71"/>
       <c r="AI246" s="29"/>
     </row>
-    <row r="247" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="247" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="29"/>
       <c r="B247" s="29"/>
       <c r="C247" s="29"/>
@@ -10545,7 +10554,7 @@
       <c r="AH247" s="71"/>
       <c r="AI247" s="29"/>
     </row>
-    <row r="248" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="248" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="29"/>
       <c r="B248" s="29"/>
       <c r="C248" s="29"/>
@@ -10584,7 +10593,7 @@
       <c r="AH248" s="71"/>
       <c r="AI248" s="29"/>
     </row>
-    <row r="249" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="249" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="29"/>
       <c r="B249" s="29"/>
       <c r="C249" s="29"/>
@@ -10623,7 +10632,7 @@
       <c r="AH249" s="71"/>
       <c r="AI249" s="29"/>
     </row>
-    <row r="250" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="250" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="29"/>
       <c r="B250" s="29"/>
       <c r="C250" s="29"/>
@@ -10662,7 +10671,7 @@
       <c r="AH250" s="71"/>
       <c r="AI250" s="29"/>
     </row>
-    <row r="251" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="251" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="29"/>
       <c r="B251" s="29"/>
       <c r="C251" s="29"/>
@@ -10701,7 +10710,7 @@
       <c r="AH251" s="71"/>
       <c r="AI251" s="29"/>
     </row>
-    <row r="252" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="252" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="29"/>
       <c r="B252" s="29"/>
       <c r="C252" s="29"/>
@@ -10740,7 +10749,7 @@
       <c r="AH252" s="71"/>
       <c r="AI252" s="29"/>
     </row>
-    <row r="253" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="253" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="29"/>
       <c r="B253" s="29"/>
       <c r="C253" s="29"/>
@@ -10779,7 +10788,7 @@
       <c r="AH253" s="90"/>
       <c r="AI253" s="29"/>
     </row>
-    <row r="254" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="254" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="29"/>
       <c r="B254" s="29"/>
       <c r="C254" s="29"/>
@@ -10822,7 +10831,7 @@
       <c r="AH254" s="71"/>
       <c r="AI254" s="29"/>
     </row>
-    <row r="255" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="255" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A255" s="29"/>
       <c r="B255" s="29"/>
       <c r="C255" s="29"/>
@@ -10863,7 +10872,7 @@
       <c r="AH255" s="90"/>
       <c r="AI255" s="29"/>
     </row>
-    <row r="256" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="256" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A256" s="29"/>
       <c r="B256" s="29"/>
       <c r="C256" s="29"/>
@@ -10900,7 +10909,7 @@
       <c r="AH256" s="29"/>
       <c r="AI256" s="29"/>
     </row>
-    <row r="257" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="257" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A257" s="29"/>
       <c r="B257" s="29"/>
       <c r="C257" s="29"/>
@@ -10910,7 +10919,7 @@
         <v>52</v>
       </c>
       <c r="G257" s="29" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="H257" s="29"/>
       <c r="I257" s="29"/>
@@ -10941,7 +10950,7 @@
       <c r="AH257" s="29"/>
       <c r="AI257" s="29"/>
     </row>
-    <row r="258" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="258" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A258" s="29"/>
       <c r="B258" s="29"/>
       <c r="C258" s="29"/>
@@ -10980,7 +10989,7 @@
       <c r="AH258" s="29"/>
       <c r="AI258" s="29"/>
     </row>
-    <row r="259" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="259" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A259" s="29"/>
       <c r="B259" s="29"/>
       <c r="C259" s="29"/>
@@ -11017,7 +11026,7 @@
       <c r="AH259" s="29"/>
       <c r="AI259" s="29"/>
     </row>
-    <row r="260" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="260" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A260" s="29"/>
       <c r="B260" s="29"/>
       <c r="C260" s="29"/>
@@ -11059,7 +11068,7 @@
       <c r="AH260" s="29"/>
       <c r="AI260" s="29"/>
     </row>
-    <row r="261" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="261" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A261" s="29"/>
       <c r="B261" s="29"/>
       <c r="C261" s="29"/>
@@ -11098,7 +11107,7 @@
       <c r="AH261" s="29"/>
       <c r="AI261" s="29"/>
     </row>
-    <row r="262" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="262" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A262" s="29"/>
       <c r="B262" s="29"/>
       <c r="C262" s="29"/>
@@ -11135,7 +11144,7 @@
       <c r="AH262" s="29"/>
       <c r="AI262" s="29"/>
     </row>
-    <row r="263" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="263" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A263" s="29"/>
       <c r="B263" s="29"/>
       <c r="C263" s="29"/>
@@ -11176,7 +11185,7 @@
       <c r="AH263" s="29"/>
       <c r="AI263" s="29"/>
     </row>
-    <row r="264" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="264" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A264" s="29"/>
       <c r="B264" s="29"/>
       <c r="C264" s="29"/>
@@ -11215,7 +11224,7 @@
       <c r="AH264" s="29"/>
       <c r="AI264" s="29"/>
     </row>
-    <row r="265" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="265" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A265" s="29"/>
       <c r="B265" s="29"/>
       <c r="C265" s="29"/>
@@ -11254,7 +11263,7 @@
       <c r="AH265" s="29"/>
       <c r="AI265" s="29"/>
     </row>
-    <row r="266" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="266" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A266" s="29"/>
       <c r="B266" s="29"/>
       <c r="C266" s="29"/>
@@ -11293,7 +11302,7 @@
       <c r="AH266" s="29"/>
       <c r="AI266" s="29"/>
     </row>
-    <row r="267" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="267" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A267" s="29"/>
       <c r="B267" s="29"/>
       <c r="C267" s="29"/>
@@ -11332,7 +11341,7 @@
       <c r="AH267" s="29"/>
       <c r="AI267" s="29"/>
     </row>
-    <row r="268" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="268" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A268" s="29"/>
       <c r="B268" s="29"/>
       <c r="C268" s="29"/>
@@ -11371,7 +11380,7 @@
       <c r="AH268" s="29"/>
       <c r="AI268" s="29"/>
     </row>
-    <row r="269" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="269" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A269" s="29"/>
       <c r="B269" s="29"/>
       <c r="C269" s="29"/>
@@ -11408,7 +11417,7 @@
       <c r="AH269" s="29"/>
       <c r="AI269" s="29"/>
     </row>
-    <row r="270" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="270" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A270" s="29"/>
       <c r="B270" s="29"/>
       <c r="C270" s="29"/>
@@ -11449,7 +11458,7 @@
       <c r="AH270" s="29"/>
       <c r="AI270" s="29"/>
     </row>
-    <row r="271" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="271" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A271" s="29"/>
       <c r="B271" s="29"/>
       <c r="C271" s="29"/>
@@ -11488,7 +11497,7 @@
       <c r="AH271" s="29"/>
       <c r="AI271" s="29"/>
     </row>
-    <row r="272" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="272" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A272" s="29"/>
       <c r="B272" s="29"/>
       <c r="C272" s="29"/>
@@ -11527,7 +11536,7 @@
       <c r="AH272" s="29"/>
       <c r="AI272" s="29"/>
     </row>
-    <row r="273" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="273" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A273" s="29"/>
       <c r="B273" s="29"/>
       <c r="C273" s="29"/>
@@ -11566,7 +11575,7 @@
       <c r="AH273" s="29"/>
       <c r="AI273" s="29"/>
     </row>
-    <row r="274" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="274" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A274" s="29"/>
       <c r="B274" s="29"/>
       <c r="C274" s="29"/>
@@ -11603,7 +11612,7 @@
       <c r="AH274" s="29"/>
       <c r="AI274" s="29"/>
     </row>
-    <row r="275" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="275" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A275" s="29"/>
       <c r="B275" s="29"/>
       <c r="C275" s="29"/>
@@ -11642,7 +11651,7 @@
       <c r="AH275" s="29"/>
       <c r="AI275" s="29"/>
     </row>
-    <row r="276" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="276" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A276" s="29"/>
       <c r="B276" s="29"/>
       <c r="C276" s="29"/>
@@ -11683,7 +11692,7 @@
       <c r="AH276" s="37"/>
       <c r="AI276" s="29"/>
     </row>
-    <row r="277" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="277" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A277" s="29"/>
       <c r="B277" s="29"/>
       <c r="C277" s="29"/>
@@ -11724,7 +11733,7 @@
       <c r="AH277" s="31"/>
       <c r="AI277" s="29"/>
     </row>
-    <row r="278" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="278" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A278" s="29"/>
       <c r="B278" s="29"/>
       <c r="C278" s="29"/>
@@ -11763,7 +11772,7 @@
       <c r="AH278" s="34"/>
       <c r="AI278" s="29"/>
     </row>
-    <row r="279" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="279" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A279" s="29"/>
       <c r="B279" s="29"/>
       <c r="C279" s="29"/>
@@ -11804,7 +11813,7 @@
       <c r="AH279" s="31"/>
       <c r="AI279" s="29"/>
     </row>
-    <row r="280" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="280" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A280" s="29"/>
       <c r="B280" s="29"/>
       <c r="C280" s="29"/>
@@ -11843,7 +11852,7 @@
       <c r="AH280" s="31"/>
       <c r="AI280" s="29"/>
     </row>
-    <row r="281" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="281" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A281" s="29"/>
       <c r="B281" s="29"/>
       <c r="C281" s="29"/>
@@ -11882,7 +11891,7 @@
       <c r="AH281" s="34"/>
       <c r="AI281" s="29"/>
     </row>
-    <row r="282" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="282" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A282" s="29"/>
       <c r="B282" s="29"/>
       <c r="C282" s="29"/>
@@ -11919,7 +11928,7 @@
       <c r="AH282" s="55"/>
       <c r="AI282" s="29"/>
     </row>
-    <row r="283" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="283" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A283" s="29"/>
       <c r="B283" s="29"/>
       <c r="C283" s="29"/>
@@ -11958,7 +11967,7 @@
       <c r="AH283" s="55"/>
       <c r="AI283" s="29"/>
     </row>
-    <row r="284" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="284" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A284" s="29"/>
       <c r="B284" s="29"/>
       <c r="C284" s="29"/>
@@ -11995,7 +12004,7 @@
       <c r="AH284" s="55"/>
       <c r="AI284" s="29"/>
     </row>
-    <row r="285" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="285" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A285" s="29"/>
       <c r="B285" s="29"/>
       <c r="C285" s="29"/>
@@ -12034,7 +12043,7 @@
       <c r="AH285" s="55"/>
       <c r="AI285" s="29"/>
     </row>
-    <row r="286" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="286" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A286" s="29"/>
       <c r="B286" s="29"/>
       <c r="C286" s="29"/>
@@ -12073,7 +12082,7 @@
       <c r="AH286" s="55"/>
       <c r="AI286" s="29"/>
     </row>
-    <row r="287" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="287" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A287" s="29"/>
       <c r="B287" s="29"/>
       <c r="C287" s="29"/>
@@ -12110,7 +12119,7 @@
       <c r="AH287" s="55"/>
       <c r="AI287" s="29"/>
     </row>
-    <row r="288" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="288" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A288" s="29"/>
       <c r="B288" s="29"/>
       <c r="C288" s="29"/>
@@ -12149,7 +12158,7 @@
       <c r="AH288" s="55"/>
       <c r="AI288" s="29"/>
     </row>
-    <row r="289" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="289" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A289" s="29"/>
       <c r="B289" s="29"/>
       <c r="C289" s="29"/>
@@ -12188,7 +12197,7 @@
       <c r="AH289" s="55"/>
       <c r="AI289" s="29"/>
     </row>
-    <row r="290" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="290" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A290" s="29"/>
       <c r="B290" s="29"/>
       <c r="C290" s="29"/>
@@ -12227,7 +12236,7 @@
       <c r="AH290" s="55"/>
       <c r="AI290" s="29"/>
     </row>
-    <row r="291" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="291" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A291" s="29"/>
       <c r="B291" s="29"/>
       <c r="C291" s="29"/>
@@ -12266,7 +12275,7 @@
       <c r="AH291" s="55"/>
       <c r="AI291" s="29"/>
     </row>
-    <row r="292" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="292" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A292" s="29"/>
       <c r="B292" s="29"/>
       <c r="C292" s="29"/>
@@ -12303,7 +12312,7 @@
       <c r="AH292" s="29"/>
       <c r="AI292" s="29"/>
     </row>
-    <row r="293" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="293" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D293" s="42" t="str">
         <f>$C$7&amp;"9."</f>
         <v>3.1.9.</v>
@@ -12312,10 +12321,10 @@
         <v>150</v>
       </c>
     </row>
-    <row r="294" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="294" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D294" s="42"/>
     </row>
-    <row r="295" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="295" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D295" s="42"/>
       <c r="E295" s="42" t="str">
         <f>$D$293&amp;"1."</f>
@@ -12326,13 +12335,13 @@
         <v>URL設計概要</v>
       </c>
     </row>
-    <row r="296" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="296" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D296" s="42"/>
       <c r="F296" s="41" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="297" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="297" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D297" s="42"/>
       <c r="F297" s="41" t="s">
         <v>148</v>
@@ -12341,10 +12350,10 @@
         <v>147</v>
       </c>
     </row>
-    <row r="298" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="298" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D298" s="42"/>
     </row>
-    <row r="299" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="299" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D299" s="42"/>
       <c r="E299" s="42" t="str">
         <f>$D$293&amp;"2."</f>
@@ -12355,13 +12364,13 @@
         <v>URL設計方針</v>
       </c>
     </row>
-    <row r="300" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="300" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D300" s="42"/>
       <c r="F300" s="41" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="301" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="301" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D301" s="42"/>
       <c r="F301" s="52" t="s">
         <v>146</v>
@@ -12396,7 +12405,7 @@
       <c r="AF301" s="53"/>
       <c r="AG301" s="54"/>
     </row>
-    <row r="302" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="302" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D302" s="42"/>
       <c r="F302" s="69" t="s">
         <v>145</v>
@@ -12431,7 +12440,7 @@
       <c r="AF302" s="98"/>
       <c r="AG302" s="100"/>
     </row>
-    <row r="303" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="303" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D303" s="42"/>
       <c r="F303" s="81"/>
       <c r="G303" s="101"/>
@@ -12464,10 +12473,10 @@
       <c r="AF303" s="101"/>
       <c r="AG303" s="102"/>
     </row>
-    <row r="304" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="304" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D304" s="42"/>
     </row>
-    <row r="305" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="305" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D305" s="42"/>
       <c r="E305" s="42" t="str">
         <f>$D$293&amp;"3."</f>
@@ -12478,7 +12487,7 @@
         <v>URL設計詳細</v>
       </c>
     </row>
-    <row r="306" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="306" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D306" s="42"/>
       <c r="F306" s="29" t="s">
         <v>189</v>
@@ -12486,52 +12495,52 @@
       <c r="G306" s="29"/>
       <c r="H306" s="29"/>
     </row>
-    <row r="307" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="307" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D307" s="42"/>
       <c r="F307" s="29"/>
       <c r="G307" s="29"/>
       <c r="H307" s="29"/>
     </row>
-    <row r="308" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="308" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D308" s="42"/>
       <c r="F308" s="29"/>
       <c r="G308" s="29"/>
       <c r="H308" s="29"/>
     </row>
-    <row r="309" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="309" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D309" s="42"/>
       <c r="F309" s="29"/>
       <c r="G309" s="29"/>
       <c r="H309" s="29"/>
     </row>
-    <row r="310" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="310" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D310" s="42"/>
       <c r="F310" s="29"/>
       <c r="G310" s="29"/>
       <c r="H310" s="29"/>
     </row>
-    <row r="311" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="311" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D311" s="42"/>
       <c r="F311" s="29"/>
       <c r="G311" s="29"/>
       <c r="H311" s="29"/>
     </row>
-    <row r="312" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="312" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D312" s="42"/>
       <c r="F312" s="29"/>
       <c r="G312" s="29"/>
       <c r="H312" s="29"/>
     </row>
-    <row r="313" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="313" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D313" s="42"/>
     </row>
-    <row r="314" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="314" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D314" s="42"/>
     </row>
-    <row r="315" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="315" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D315" s="42"/>
     </row>
-    <row r="316" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="316" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E316" s="42"/>
       <c r="F316" s="87"/>
       <c r="G316" s="52" t="s">
@@ -12565,7 +12574,7 @@
       <c r="AE316" s="53"/>
       <c r="AF316" s="54"/>
     </row>
-    <row r="317" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="317" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E317" s="42"/>
       <c r="F317" s="86" t="s">
         <v>134</v>
@@ -12601,7 +12610,7 @@
       <c r="AE317" s="49"/>
       <c r="AF317" s="50"/>
     </row>
-    <row r="318" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="318" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E318" s="42"/>
       <c r="F318" s="84"/>
       <c r="G318" s="46"/>
@@ -12631,7 +12640,7 @@
       <c r="AE318" s="47"/>
       <c r="AF318" s="51"/>
     </row>
-    <row r="319" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="319" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E319" s="42"/>
       <c r="F319" s="86" t="s">
         <v>132</v>
@@ -12667,7 +12676,7 @@
       <c r="AE319" s="49"/>
       <c r="AF319" s="50"/>
     </row>
-    <row r="320" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="320" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E320" s="42"/>
       <c r="F320" s="84"/>
       <c r="G320" s="46"/>
@@ -12697,7 +12706,7 @@
       <c r="AE320" s="47"/>
       <c r="AF320" s="51"/>
     </row>
-    <row r="321" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="321" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E321" s="42"/>
       <c r="F321" s="86" t="s">
         <v>61</v>
@@ -12733,7 +12742,7 @@
       <c r="AE321" s="49"/>
       <c r="AF321" s="50"/>
     </row>
-    <row r="322" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="322" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E322" s="42"/>
       <c r="F322" s="89"/>
       <c r="G322" s="43"/>
@@ -12765,7 +12774,7 @@
       <c r="AE322" s="44"/>
       <c r="AF322" s="45"/>
     </row>
-    <row r="323" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="323" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E323" s="42"/>
       <c r="F323" s="84"/>
       <c r="G323" s="46"/>
@@ -12795,7 +12804,7 @@
       <c r="AE323" s="47"/>
       <c r="AF323" s="51"/>
     </row>
-    <row r="324" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="324" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E324" s="42"/>
       <c r="F324" s="85" t="s">
         <v>62</v>
@@ -12831,7 +12840,7 @@
       <c r="AE324" s="49"/>
       <c r="AF324" s="50"/>
     </row>
-    <row r="325" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="325" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E325" s="66"/>
       <c r="F325" s="88"/>
       <c r="G325" s="81"/>
@@ -12861,13 +12870,13 @@
       <c r="AE325" s="47"/>
       <c r="AF325" s="51"/>
     </row>
-    <row r="326" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="326" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D326" s="42"/>
       <c r="E326" s="36"/>
       <c r="F326" s="36"/>
       <c r="G326" s="36"/>
     </row>
-    <row r="327" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="327" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D327" s="42"/>
       <c r="E327" s="36"/>
       <c r="F327" s="36" t="s">
@@ -12875,7 +12884,7 @@
       </c>
       <c r="G327" s="36"/>
     </row>
-    <row r="328" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="328" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D328" s="42"/>
       <c r="E328" s="36"/>
       <c r="F328" s="36" t="s">
@@ -12883,12 +12892,12 @@
       </c>
       <c r="G328" s="36"/>
     </row>
-    <row r="329" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="329" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D329" s="42"/>
     </row>
-    <row r="330" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="331" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="332" spans="4:32" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="330" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="331" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="332" spans="4:32" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D332" s="28" t="str">
         <f>$C$7&amp;"10."</f>
         <v>3.1.10.</v>
@@ -12897,7 +12906,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="333" spans="4:32" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="333" spans="4:32" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D333" s="28"/>
       <c r="E333" s="28" t="str">
         <f>D332&amp;"1."</f>
@@ -12908,29 +12917,29 @@
         <v>コンテンツ更新機能概要</v>
       </c>
     </row>
-    <row r="334" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="334" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D334" s="42"/>
       <c r="E334" s="42"/>
       <c r="F334" s="41" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="335" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="335" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D335" s="42"/>
       <c r="E335" s="42"/>
       <c r="F335" s="41" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="336" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="F336" s="36" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="336" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="F336" s="36" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="337" spans="5:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="337" spans="5:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F337" s="36"/>
     </row>
-    <row r="338" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="338" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F338" s="19"/>
       <c r="G338" s="19"/>
       <c r="H338" s="19"/>
@@ -12961,7 +12970,7 @@
       <c r="AG338" s="19"/>
       <c r="AH338" s="19"/>
     </row>
-    <row r="339" spans="5:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="339" spans="5:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E339" s="42" t="str">
         <f>D332&amp;"2."</f>
         <v>3.1.10.2.</v>
@@ -12999,12 +13008,12 @@
       <c r="AG339" s="44"/>
       <c r="AH339" s="44"/>
     </row>
-    <row r="340" spans="5:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="340" spans="5:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F340" s="41" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="341" spans="5:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="341" spans="5:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F341" s="52" t="s">
         <v>50</v>
       </c>
@@ -13041,7 +13050,7 @@
       <c r="AG341" s="53"/>
       <c r="AH341" s="54"/>
     </row>
-    <row r="342" spans="5:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="342" spans="5:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F342" s="81" t="s">
         <v>161</v>
       </c>
@@ -13078,7 +13087,7 @@
       <c r="AG342" s="101"/>
       <c r="AH342" s="102"/>
     </row>
-    <row r="343" spans="5:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="343" spans="5:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F343" s="70"/>
       <c r="G343" s="70"/>
       <c r="H343" s="70"/>
@@ -13109,7 +13118,7 @@
       <c r="AG343" s="44"/>
       <c r="AH343" s="44"/>
     </row>
-    <row r="344" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="344" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="E344" s="28" t="str">
         <f>D332&amp;"3."</f>
         <v>3.1.10.3.</v>
@@ -13124,7 +13133,7 @@
       <c r="K344" s="36"/>
       <c r="L344" s="36"/>
     </row>
-    <row r="345" spans="5:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="345" spans="5:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F345" s="77" t="s">
         <v>41</v>
       </c>
@@ -13138,7 +13147,7 @@
       <c r="K345" s="74"/>
       <c r="L345" s="74"/>
     </row>
-    <row r="346" spans="5:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="346" spans="5:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F346" s="77"/>
       <c r="G346" s="79" t="s">
         <v>120</v>
@@ -13151,7 +13160,7 @@
       <c r="K346" s="74"/>
       <c r="L346" s="74"/>
     </row>
-    <row r="347" spans="5:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="347" spans="5:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F347" s="77"/>
       <c r="G347" s="79"/>
       <c r="H347" s="79" t="s">
@@ -13164,7 +13173,7 @@
       <c r="K347" s="74"/>
       <c r="L347" s="74"/>
     </row>
-    <row r="348" spans="5:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="348" spans="5:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F348" s="77"/>
       <c r="G348" s="79" t="s">
         <v>54</v>
@@ -13177,7 +13186,7 @@
       <c r="K348" s="74"/>
       <c r="L348" s="74"/>
     </row>
-    <row r="349" spans="5:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="349" spans="5:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F349" s="77"/>
       <c r="G349" s="74"/>
       <c r="H349" s="79" t="s">
@@ -13190,7 +13199,7 @@
       <c r="K349" s="74"/>
       <c r="L349" s="74"/>
     </row>
-    <row r="350" spans="5:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="350" spans="5:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F350" s="77"/>
       <c r="G350" s="74"/>
       <c r="H350" s="79" t="s">
@@ -13203,7 +13212,7 @@
       <c r="K350" s="74"/>
       <c r="L350" s="74"/>
     </row>
-    <row r="351" spans="5:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="351" spans="5:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F351" s="74"/>
       <c r="G351" s="79" t="s">
         <v>120</v>
@@ -13216,7 +13225,7 @@
       <c r="K351" s="74"/>
       <c r="L351" s="74"/>
     </row>
-    <row r="352" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="352" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F352" s="36"/>
       <c r="G352" s="36"/>
       <c r="H352" s="82" t="s">
@@ -13229,7 +13238,7 @@
       <c r="K352" s="36"/>
       <c r="L352" s="36"/>
     </row>
-    <row r="353" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="353" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F353" s="36"/>
       <c r="G353" s="83"/>
       <c r="H353" s="73" t="s">
@@ -13242,7 +13251,7 @@
       <c r="K353" s="36"/>
       <c r="L353" s="36"/>
     </row>
-    <row r="354" spans="4:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="354" spans="4:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F354" s="36"/>
       <c r="G354" s="83"/>
       <c r="H354" s="36"/>
@@ -13251,7 +13260,7 @@
       <c r="K354" s="36"/>
       <c r="L354" s="36"/>
     </row>
-    <row r="355" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="355" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D355" s="28" t="str">
         <f>$C$7&amp;"11."</f>
         <v>3.1.11.</v>
@@ -13260,7 +13269,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="356" spans="4:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="356" spans="4:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D356" s="42"/>
       <c r="E356" s="42" t="str">
         <f>D355&amp;"1."</f>
@@ -13270,22 +13279,22 @@
         <v>200</v>
       </c>
     </row>
-    <row r="357" spans="4:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="357" spans="4:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D357" s="42"/>
       <c r="E357" s="41" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="358" spans="4:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="358" spans="4:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D358" s="42"/>
       <c r="E358" s="41" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="359" spans="4:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="359" spans="4:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D359" s="42"/>
     </row>
-    <row r="360" spans="4:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="360" spans="4:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D360" s="42"/>
       <c r="E360" s="42" t="str">
         <f>D355&amp;"2."</f>
@@ -13295,13 +13304,13 @@
         <v>201</v>
       </c>
     </row>
-    <row r="361" spans="4:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="361" spans="4:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D361" s="42"/>
       <c r="E361" s="41" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="362" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="362" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F362" s="19"/>
       <c r="G362" s="19"/>
       <c r="H362" s="19"/>
@@ -13332,43 +13341,43 @@
       <c r="AG362" s="19"/>
       <c r="AH362" s="19"/>
     </row>
-    <row r="363" spans="4:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="363" spans="4:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D363" s="42" t="str">
         <f>$C$7&amp;"12."</f>
         <v>3.1.12.</v>
       </c>
       <c r="E363" s="41" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="364" spans="4:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="364" spans="4:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D364" s="42"/>
       <c r="E364" s="41" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="365" spans="4:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="365" spans="4:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D365" s="42"/>
       <c r="E365" s="41" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="366" spans="4:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="366" spans="4:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D366" s="42"/>
     </row>
-    <row r="367" spans="4:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="367" spans="4:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D367" s="42"/>
       <c r="E367" s="41" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="368" spans="4:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="368" spans="4:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D368" s="42"/>
       <c r="E368" s="41" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="369" spans="6:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="369" spans="6:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F369" s="70"/>
       <c r="G369" s="70"/>
       <c r="H369" s="70"/>
@@ -13399,7 +13408,7 @@
       <c r="AG369" s="44"/>
       <c r="AH369" s="44"/>
     </row>
-    <row r="370" spans="6:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="370" spans="6:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="F370" s="91"/>
     </row>
   </sheetData>

--- a/nablarch_sample/アプリケーション方式設計書_3画面処理方式_3.1同期処理方式.xlsx
+++ b/nablarch_sample/アプリケーション方式設計書_3画面処理方式_3.1同期処理方式.xlsx
@@ -1,21 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26731"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB1EAFF9-996A-4E6D-9EC7-2263D852D581}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26130"/>
+  <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7F1F781-94DE-42A2-A8A0-87833597E3FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" tabRatio="668" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1245" yWindow="-120" windowWidth="27675" windowHeight="16440" tabRatio="668" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="3.1.同期処理方式" sheetId="2" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'3.1.同期処理方式'!#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'3.1.同期処理方式'!$A$1:$AI$369</definedName>
-    <definedName name="Z_AC3D26AC_6835_49DE_BCEC_94F40C257790_.wvu.PrintArea" localSheetId="0" hidden="1">'3.1.同期処理方式'!$A$1:$AI$292</definedName>
-    <definedName name="Z_B9596DFB_62BC_4685_B6E9_D37718868A8E_.wvu.PrintArea" localSheetId="0" hidden="1">'3.1.同期処理方式'!$A$1:$AI$292</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -4041,6 +4035,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="7" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="7" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -4106,12 +4106,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="7" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="7" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="8">
@@ -4171,8 +4165,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="1266825" y="43109874"/>
-          <a:ext cx="7172324" cy="768626"/>
+          <a:off x="1362075" y="44084599"/>
+          <a:ext cx="7810499" cy="787676"/>
           <a:chOff x="1362075" y="5760869"/>
           <a:chExt cx="7810499" cy="820906"/>
         </a:xfrm>
@@ -5023,150 +5017,150 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
+  <sheetPr codeName="Sheet1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AI370"/>
-  <sheetFormatPr defaultColWidth="3.6328125" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="3.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="16384" width="3.6328125" style="4"/>
+    <col min="1" max="16384" width="3.625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="3"/>
-      <c r="E1" s="112" t="s">
+      <c r="E1" s="114" t="s">
         <v>156</v>
       </c>
-      <c r="F1" s="113"/>
-      <c r="G1" s="113"/>
-      <c r="H1" s="113"/>
-      <c r="I1" s="113"/>
-      <c r="J1" s="113"/>
-      <c r="K1" s="113"/>
-      <c r="L1" s="113"/>
-      <c r="M1" s="113"/>
-      <c r="N1" s="113"/>
-      <c r="O1" s="114"/>
+      <c r="F1" s="115"/>
+      <c r="G1" s="115"/>
+      <c r="H1" s="115"/>
+      <c r="I1" s="115"/>
+      <c r="J1" s="115"/>
+      <c r="K1" s="115"/>
+      <c r="L1" s="115"/>
+      <c r="M1" s="115"/>
+      <c r="N1" s="115"/>
+      <c r="O1" s="116"/>
       <c r="P1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="Q1" s="2"/>
-      <c r="R1" s="115" t="s">
+      <c r="R1" s="117" t="s">
         <v>155</v>
       </c>
-      <c r="S1" s="116"/>
-      <c r="T1" s="116"/>
-      <c r="U1" s="116"/>
-      <c r="V1" s="116"/>
-      <c r="W1" s="116"/>
-      <c r="X1" s="117"/>
+      <c r="S1" s="118"/>
+      <c r="T1" s="118"/>
+      <c r="U1" s="118"/>
+      <c r="V1" s="118"/>
+      <c r="W1" s="118"/>
+      <c r="X1" s="119"/>
       <c r="Y1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="Z1" s="3"/>
-      <c r="AA1" s="118"/>
-      <c r="AB1" s="119"/>
-      <c r="AC1" s="119"/>
-      <c r="AD1" s="119"/>
-      <c r="AE1" s="120"/>
-      <c r="AF1" s="109"/>
-      <c r="AG1" s="110"/>
-      <c r="AH1" s="110"/>
-      <c r="AI1" s="111"/>
-    </row>
-    <row r="2" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AA1" s="120"/>
+      <c r="AB1" s="121"/>
+      <c r="AC1" s="121"/>
+      <c r="AD1" s="121"/>
+      <c r="AE1" s="122"/>
+      <c r="AF1" s="111"/>
+      <c r="AG1" s="112"/>
+      <c r="AH1" s="112"/>
+      <c r="AI1" s="113"/>
+    </row>
+    <row r="2" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="5" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
       <c r="D2" s="7"/>
-      <c r="E2" s="121"/>
-      <c r="F2" s="122"/>
-      <c r="G2" s="122"/>
-      <c r="H2" s="122"/>
-      <c r="I2" s="122"/>
-      <c r="J2" s="122"/>
-      <c r="K2" s="122"/>
-      <c r="L2" s="122"/>
-      <c r="M2" s="122"/>
-      <c r="N2" s="122"/>
-      <c r="O2" s="123"/>
+      <c r="E2" s="123"/>
+      <c r="F2" s="124"/>
+      <c r="G2" s="124"/>
+      <c r="H2" s="124"/>
+      <c r="I2" s="124"/>
+      <c r="J2" s="124"/>
+      <c r="K2" s="124"/>
+      <c r="L2" s="124"/>
+      <c r="M2" s="124"/>
+      <c r="N2" s="124"/>
+      <c r="O2" s="125"/>
       <c r="P2" s="8" t="s">
         <v>12</v>
       </c>
       <c r="Q2" s="9"/>
-      <c r="R2" s="124" t="s">
+      <c r="R2" s="126" t="s">
         <v>3</v>
       </c>
-      <c r="S2" s="125"/>
-      <c r="T2" s="125"/>
-      <c r="U2" s="125"/>
-      <c r="V2" s="125"/>
-      <c r="W2" s="125"/>
-      <c r="X2" s="126"/>
+      <c r="S2" s="127"/>
+      <c r="T2" s="127"/>
+      <c r="U2" s="127"/>
+      <c r="V2" s="127"/>
+      <c r="W2" s="127"/>
+      <c r="X2" s="128"/>
       <c r="Y2" s="1" t="s">
         <v>4</v>
       </c>
       <c r="Z2" s="3"/>
-      <c r="AA2" s="118"/>
-      <c r="AB2" s="119"/>
-      <c r="AC2" s="119"/>
-      <c r="AD2" s="119"/>
-      <c r="AE2" s="120"/>
-      <c r="AF2" s="109"/>
-      <c r="AG2" s="110"/>
-      <c r="AH2" s="110"/>
-      <c r="AI2" s="111"/>
-    </row>
-    <row r="3" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AA2" s="120"/>
+      <c r="AB2" s="121"/>
+      <c r="AC2" s="121"/>
+      <c r="AD2" s="121"/>
+      <c r="AE2" s="122"/>
+      <c r="AF2" s="111"/>
+      <c r="AG2" s="112"/>
+      <c r="AH2" s="112"/>
+      <c r="AI2" s="113"/>
+    </row>
+    <row r="3" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B3" s="10"/>
       <c r="C3" s="11"/>
       <c r="D3" s="3"/>
-      <c r="E3" s="130"/>
-      <c r="F3" s="130"/>
-      <c r="G3" s="130"/>
-      <c r="H3" s="130"/>
-      <c r="I3" s="130"/>
-      <c r="J3" s="130"/>
-      <c r="K3" s="130"/>
-      <c r="L3" s="130"/>
-      <c r="M3" s="130"/>
-      <c r="N3" s="130"/>
-      <c r="O3" s="130"/>
+      <c r="E3" s="132"/>
+      <c r="F3" s="132"/>
+      <c r="G3" s="132"/>
+      <c r="H3" s="132"/>
+      <c r="I3" s="132"/>
+      <c r="J3" s="132"/>
+      <c r="K3" s="132"/>
+      <c r="L3" s="132"/>
+      <c r="M3" s="132"/>
+      <c r="N3" s="132"/>
+      <c r="O3" s="132"/>
       <c r="P3" s="12"/>
       <c r="Q3" s="13"/>
-      <c r="R3" s="127"/>
-      <c r="S3" s="128"/>
-      <c r="T3" s="128"/>
-      <c r="U3" s="128"/>
-      <c r="V3" s="128"/>
-      <c r="W3" s="128"/>
-      <c r="X3" s="129"/>
+      <c r="R3" s="129"/>
+      <c r="S3" s="130"/>
+      <c r="T3" s="130"/>
+      <c r="U3" s="130"/>
+      <c r="V3" s="130"/>
+      <c r="W3" s="130"/>
+      <c r="X3" s="131"/>
       <c r="Y3" s="12" t="s">
         <v>6</v>
       </c>
       <c r="Z3" s="14"/>
-      <c r="AA3" s="118"/>
-      <c r="AB3" s="119"/>
-      <c r="AC3" s="119"/>
-      <c r="AD3" s="119"/>
-      <c r="AE3" s="120"/>
-      <c r="AF3" s="109"/>
-      <c r="AG3" s="110"/>
-      <c r="AH3" s="110"/>
-      <c r="AI3" s="111"/>
-    </row>
-    <row r="4" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="5" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AA3" s="120"/>
+      <c r="AB3" s="121"/>
+      <c r="AC3" s="121"/>
+      <c r="AD3" s="121"/>
+      <c r="AE3" s="122"/>
+      <c r="AF3" s="111"/>
+      <c r="AG3" s="112"/>
+      <c r="AH3" s="112"/>
+      <c r="AI3" s="113"/>
+    </row>
+    <row r="4" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="5" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B5" s="15" t="s">
         <v>13</v>
       </c>
@@ -5174,8 +5168,8 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="7" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="7" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C7" s="15" t="str">
         <f>$B$5&amp;"1."</f>
         <v>3.1.</v>
@@ -5184,8 +5178,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="9" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="9" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D9" s="28" t="str">
         <f>$C$7&amp;"1."</f>
         <v>3.1.1.</v>
@@ -5194,19 +5188,19 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D10" s="15"/>
       <c r="E10" s="4" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D11" s="42"/>
       <c r="E11" s="41" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="12" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D12" s="26"/>
       <c r="E12" s="26"/>
       <c r="F12" s="26"/>
@@ -5240,7 +5234,7 @@
       <c r="AH12" s="26"/>
       <c r="AI12" s="26"/>
     </row>
-    <row r="13" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D13" s="15" t="str">
         <f>$C$7&amp;"2."</f>
         <v>3.1.2.</v>
@@ -5279,7 +5273,7 @@
       <c r="AH13" s="27"/>
       <c r="AI13" s="27"/>
     </row>
-    <row r="14" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B14" s="41"/>
       <c r="E14" s="42" t="str">
         <f>D13&amp;"1."</f>
@@ -5319,7 +5313,7 @@
       <c r="AH14" s="27"/>
       <c r="AI14" s="27"/>
     </row>
-    <row r="15" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D15" s="29"/>
       <c r="E15" s="29"/>
       <c r="F15" s="52" t="s">
@@ -5357,7 +5351,7 @@
       <c r="AH15" s="29"/>
       <c r="AI15" s="29"/>
     </row>
-    <row r="16" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D16" s="29"/>
       <c r="E16" s="29"/>
       <c r="F16" s="56" t="s">
@@ -5395,7 +5389,7 @@
       <c r="AH16" s="29"/>
       <c r="AI16" s="29"/>
     </row>
-    <row r="17" spans="4:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="4:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D17" s="29"/>
       <c r="E17" s="29"/>
       <c r="F17" s="35" t="s">
@@ -5433,7 +5427,7 @@
       <c r="AH17" s="29"/>
       <c r="AI17" s="29"/>
     </row>
-    <row r="18" spans="4:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="4:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D18" s="29"/>
       <c r="E18" s="29"/>
       <c r="F18" s="30"/>
@@ -5461,7 +5455,7 @@
       <c r="AH18" s="29"/>
       <c r="AI18" s="29"/>
     </row>
-    <row r="19" spans="4:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="4:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D19" s="29"/>
       <c r="E19" s="29"/>
       <c r="F19" s="32"/>
@@ -5497,7 +5491,7 @@
       <c r="AH19" s="29"/>
       <c r="AI19" s="29"/>
     </row>
-    <row r="20" spans="4:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="4:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D20" s="42"/>
       <c r="F20" s="27"/>
       <c r="G20" s="27"/>
@@ -5530,8 +5524,8 @@
       <c r="AH20" s="27"/>
       <c r="AI20" s="27"/>
     </row>
-    <row r="21" spans="4:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="22" spans="4:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="4:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="22" spans="4:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D22" s="28" t="str">
         <f>$C$7&amp;"3."</f>
         <v>3.1.3.</v>
@@ -5540,7 +5534,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="4:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="4:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D23" s="28"/>
       <c r="E23" s="28" t="str">
         <f>$D$22&amp;"1."</f>
@@ -5551,28 +5545,28 @@
         <v>ブラウザキャッシュ制御機能概要</v>
       </c>
     </row>
-    <row r="24" spans="4:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="4:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F24" s="4" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="25" spans="4:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="4:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F25" s="41" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="26" spans="4:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="4:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F26" s="36" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="27" spans="4:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="4:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F27" s="36" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="28" spans="4:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="29" spans="4:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="4:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="29" spans="4:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E29" s="28" t="str">
         <f>$D$22&amp;"2."</f>
         <v>3.1.3.2.</v>
@@ -5582,7 +5576,7 @@
         <v>ブラウザキャッシュ制御手段</v>
       </c>
     </row>
-    <row r="30" spans="4:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="4:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F30" s="16" t="s">
         <v>47</v>
       </c>
@@ -5617,7 +5611,7 @@
       <c r="AG30" s="53"/>
       <c r="AH30" s="54"/>
     </row>
-    <row r="31" spans="4:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="4:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F31" s="56" t="s">
         <v>51</v>
       </c>
@@ -5652,7 +5646,7 @@
       <c r="AG31" s="68"/>
       <c r="AH31" s="95"/>
     </row>
-    <row r="32" spans="4:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="4:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F32" s="35" t="s">
         <v>242</v>
       </c>
@@ -5687,7 +5681,7 @@
       <c r="AG32" s="98"/>
       <c r="AH32" s="100"/>
     </row>
-    <row r="33" spans="4:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="4:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F33" s="32"/>
       <c r="G33" s="33"/>
       <c r="H33" s="33"/>
@@ -5720,7 +5714,7 @@
       <c r="AG33" s="101"/>
       <c r="AH33" s="102"/>
     </row>
-    <row r="34" spans="4:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="4:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F34" s="55"/>
       <c r="G34" s="55"/>
       <c r="H34" s="55"/>
@@ -5751,7 +5745,7 @@
       <c r="AG34" s="55"/>
       <c r="AH34" s="55"/>
     </row>
-    <row r="35" spans="4:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="4:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E35" s="24" t="str">
         <f>$D$22&amp;"3."</f>
         <v>3.1.3.3.</v>
@@ -5760,44 +5754,44 @@
         <v>216</v>
       </c>
     </row>
-    <row r="36" spans="4:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="4:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E36" s="24"/>
       <c r="F36" s="74" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="37" spans="4:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="4:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E37" s="24"/>
       <c r="F37" s="29" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="38" spans="4:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="4:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E38" s="24"/>
     </row>
-    <row r="39" spans="4:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="4:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E39" s="24"/>
       <c r="F39" s="29" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="40" spans="4:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="4:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E40" s="24"/>
       <c r="F40" s="29" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="41" spans="4:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="4:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E41" s="24"/>
     </row>
-    <row r="42" spans="4:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="4:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E42" s="24"/>
-      <c r="F42" s="131" t="s">
+      <c r="F42" s="109" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="43" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="44" spans="4:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="44" spans="4:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D44" s="66" t="str">
         <f>$C$7&amp;"4."</f>
         <v>3.1.4.</v>
@@ -5806,7 +5800,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="45" spans="4:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="4:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D45" s="66"/>
       <c r="E45" s="66" t="str">
         <f>$D$44&amp;"1."</f>
@@ -5817,13 +5811,13 @@
         <v>オートコンプリート機能概要</v>
       </c>
     </row>
-    <row r="46" spans="4:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="4:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F46" s="36" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="47" spans="4:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="48" spans="4:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="4:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="48" spans="4:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E48" s="66" t="str">
         <f>$D$44&amp;"2."</f>
         <v>3.1.4.2.</v>
@@ -5833,12 +5827,12 @@
         <v>オートコンプリート方法</v>
       </c>
     </row>
-    <row r="49" spans="5:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="5:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F49" s="36" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="50" spans="5:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="5:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F50" s="52" t="s">
         <v>18</v>
       </c>
@@ -5873,7 +5867,7 @@
       <c r="AG50" s="53"/>
       <c r="AH50" s="54"/>
     </row>
-    <row r="51" spans="5:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="5:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F51" s="69" t="s">
         <v>17</v>
       </c>
@@ -5908,7 +5902,7 @@
       <c r="AG51" s="98"/>
       <c r="AH51" s="100"/>
     </row>
-    <row r="52" spans="5:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="5:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F52" s="81"/>
       <c r="G52" s="101"/>
       <c r="H52" s="101"/>
@@ -5941,7 +5935,7 @@
       <c r="AG52" s="101"/>
       <c r="AH52" s="102"/>
     </row>
-    <row r="53" spans="5:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="5:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F53" s="103" t="s">
         <v>16</v>
       </c>
@@ -5976,7 +5970,7 @@
       <c r="AG53" s="70"/>
       <c r="AH53" s="94"/>
     </row>
-    <row r="54" spans="5:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="5:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F54" s="103"/>
       <c r="G54" s="70"/>
       <c r="H54" s="70"/>
@@ -6009,7 +6003,7 @@
       <c r="AG54" s="70"/>
       <c r="AH54" s="94"/>
     </row>
-    <row r="55" spans="5:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="5:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F55" s="81"/>
       <c r="G55" s="101"/>
       <c r="H55" s="101"/>
@@ -6042,8 +6036,8 @@
       <c r="AG55" s="101"/>
       <c r="AH55" s="102"/>
     </row>
-    <row r="56" spans="5:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="57" spans="5:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="5:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="57" spans="5:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E57" s="66" t="str">
         <f>$D$44&amp;"3."</f>
         <v>3.1.4.3.</v>
@@ -6052,76 +6046,76 @@
         <v>216</v>
       </c>
     </row>
-    <row r="58" spans="5:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="5:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E58" s="66"/>
       <c r="F58" s="36" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="59" spans="5:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="5:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E59" s="66"/>
       <c r="F59" s="36" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="60" spans="5:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="61" spans="5:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="5:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="61" spans="5:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F61" s="36" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="62" spans="5:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="5:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F62" s="36" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="63" spans="5:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="5:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F63" s="36" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="64" spans="5:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="65" spans="4:35" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="5:34" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="65" spans="4:35" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E65" s="66"/>
       <c r="F65" s="36" t="s">
         <v>280</v>
       </c>
     </row>
-    <row r="66" spans="4:35" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="4:35" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E66" s="66"/>
       <c r="F66" s="36" t="s">
         <v>297</v>
       </c>
     </row>
-    <row r="67" spans="4:35" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="4:35" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F67" s="36" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="68" spans="4:35" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="4:35" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F68" s="36" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="69" spans="4:35" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="4:35" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F69" s="36" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="70" spans="4:35" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="71" spans="4:35" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F71" s="132" t="s">
+    <row r="70" spans="4:35" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="71" spans="4:35" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="F71" s="110" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="72" spans="4:35" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="73" spans="4:35" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="4:35" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="73" spans="4:35" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F73" s="36" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="74" spans="4:35" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="75" spans="4:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="4:35" s="36" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="75" spans="4:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D75" s="28" t="str">
         <f>$C$7&amp;"5."</f>
         <v>3.1.5.</v>
@@ -6130,7 +6124,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="76" spans="4:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="4:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D76" s="28"/>
       <c r="E76" s="28" t="str">
         <f>D75&amp;"1."</f>
@@ -6141,7 +6135,7 @@
         <v>二重サブミット防止機能概要</v>
       </c>
     </row>
-    <row r="77" spans="4:35" s="41" customFormat="1" ht="11" x14ac:dyDescent="0.2">
+    <row r="77" spans="4:35" s="41" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
       <c r="D77" s="29"/>
       <c r="F77" s="41" t="s">
         <v>195</v>
@@ -6161,7 +6155,7 @@
       <c r="AH77" s="29"/>
       <c r="AI77" s="29"/>
     </row>
-    <row r="78" spans="4:35" s="41" customFormat="1" ht="11" x14ac:dyDescent="0.2">
+    <row r="78" spans="4:35" s="41" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
       <c r="D78" s="29"/>
       <c r="F78" s="41" t="s">
         <v>196</v>
@@ -6181,7 +6175,7 @@
       <c r="AH78" s="29"/>
       <c r="AI78" s="29"/>
     </row>
-    <row r="79" spans="4:35" s="41" customFormat="1" ht="11" x14ac:dyDescent="0.2">
+    <row r="79" spans="4:35" s="41" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
       <c r="D79" s="29"/>
       <c r="F79" s="41" t="s">
         <v>197</v>
@@ -6201,8 +6195,8 @@
       <c r="AH79" s="29"/>
       <c r="AI79" s="29"/>
     </row>
-    <row r="80" spans="4:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="81" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="4:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="81" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E81" s="28" t="str">
         <f>D75&amp;"2."</f>
         <v>3.1.5.2.</v>
@@ -6212,12 +6206,12 @@
         <v>二重サブミット防止方法</v>
       </c>
     </row>
-    <row r="82" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F82" s="36" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="83" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F83" s="16" t="s">
         <v>18</v>
       </c>
@@ -6252,7 +6246,7 @@
       <c r="AG83" s="17"/>
       <c r="AH83" s="18"/>
     </row>
-    <row r="84" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C84" s="29"/>
       <c r="D84" s="29"/>
       <c r="E84" s="29"/>
@@ -6290,7 +6284,7 @@
       <c r="AG84" s="70"/>
       <c r="AH84" s="94"/>
     </row>
-    <row r="85" spans="3:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C85" s="29"/>
       <c r="D85" s="29"/>
       <c r="E85" s="29"/>
@@ -6326,7 +6320,7 @@
       <c r="AG85" s="70"/>
       <c r="AH85" s="94"/>
     </row>
-    <row r="86" spans="3:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C86" s="29"/>
       <c r="D86" s="29"/>
       <c r="E86" s="29"/>
@@ -6362,7 +6356,7 @@
       <c r="AG86" s="70"/>
       <c r="AH86" s="94"/>
     </row>
-    <row r="87" spans="3:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C87" s="29"/>
       <c r="D87" s="29"/>
       <c r="E87" s="29"/>
@@ -6398,7 +6392,7 @@
       <c r="AG87" s="70"/>
       <c r="AH87" s="94"/>
     </row>
-    <row r="88" spans="3:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C88" s="29"/>
       <c r="D88" s="29"/>
       <c r="E88" s="29"/>
@@ -6434,7 +6428,7 @@
       <c r="AG88" s="70"/>
       <c r="AH88" s="94"/>
     </row>
-    <row r="89" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C89" s="29"/>
       <c r="D89" s="29"/>
       <c r="E89" s="29"/>
@@ -6472,7 +6466,7 @@
       <c r="AG89" s="98"/>
       <c r="AH89" s="100"/>
     </row>
-    <row r="90" spans="3:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C90" s="29"/>
       <c r="D90" s="29"/>
       <c r="E90" s="29"/>
@@ -6508,7 +6502,7 @@
       <c r="AG90" s="70"/>
       <c r="AH90" s="94"/>
     </row>
-    <row r="91" spans="3:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C91" s="29"/>
       <c r="D91" s="29"/>
       <c r="E91" s="29"/>
@@ -6544,7 +6538,7 @@
       <c r="AG91" s="70"/>
       <c r="AH91" s="94"/>
     </row>
-    <row r="92" spans="3:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C92" s="29"/>
       <c r="D92" s="29"/>
       <c r="E92" s="29"/>
@@ -6580,7 +6574,7 @@
       <c r="AG92" s="101"/>
       <c r="AH92" s="102"/>
     </row>
-    <row r="93" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C93" s="29"/>
       <c r="D93" s="29"/>
       <c r="E93" s="29"/>
@@ -6614,7 +6608,7 @@
       <c r="AG93" s="19"/>
       <c r="AH93" s="19"/>
     </row>
-    <row r="94" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C94" s="29"/>
       <c r="D94" s="29"/>
       <c r="E94" s="24" t="str">
@@ -6646,7 +6640,7 @@
       <c r="Z94" s="29"/>
       <c r="AA94" s="29"/>
     </row>
-    <row r="95" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C95" s="29"/>
       <c r="D95" s="29"/>
       <c r="E95" s="29"/>
@@ -6675,7 +6669,7 @@
       <c r="Z95" s="29"/>
       <c r="AA95" s="29"/>
     </row>
-    <row r="96" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C96" s="29"/>
       <c r="D96" s="29"/>
       <c r="E96" s="29"/>
@@ -6704,7 +6698,7 @@
       <c r="Z96" s="29"/>
       <c r="AA96" s="29"/>
     </row>
-    <row r="97" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C97" s="29"/>
       <c r="D97" s="29"/>
       <c r="E97" s="29"/>
@@ -6731,7 +6725,7 @@
       <c r="Z97" s="29"/>
       <c r="AA97" s="29"/>
     </row>
-    <row r="98" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C98" s="29"/>
       <c r="D98" s="29"/>
       <c r="E98" s="29"/>
@@ -6760,8 +6754,8 @@
       <c r="Z98" s="29"/>
       <c r="AA98" s="29"/>
     </row>
-    <row r="99" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="100" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="100" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D100" s="28" t="str">
         <f>$C$7&amp;"6."</f>
         <v>3.1.6.</v>
@@ -6770,7 +6764,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="101" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D101" s="28"/>
       <c r="E101" s="28" t="str">
         <f>D100&amp;"1."</f>
@@ -6781,13 +6775,13 @@
         <v>データの保持機能概要</v>
       </c>
     </row>
-    <row r="102" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F102" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="103" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="104" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="104" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E104" s="28" t="str">
         <f>D100&amp;"2."</f>
         <v>3.1.6.2.</v>
@@ -6797,12 +6791,12 @@
         <v>データの保持方法</v>
       </c>
     </row>
-    <row r="105" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F105" s="4" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="106" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F106" s="16" t="str">
         <f>F104</f>
         <v>データの保持方法</v>
@@ -6838,7 +6832,7 @@
       <c r="AG106" s="17"/>
       <c r="AH106" s="18"/>
     </row>
-    <row r="107" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F107" s="69" t="s">
         <v>31</v>
       </c>
@@ -6873,7 +6867,7 @@
       <c r="AG107" s="70"/>
       <c r="AH107" s="94"/>
     </row>
-    <row r="108" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F108" s="103"/>
       <c r="G108" s="101"/>
       <c r="H108" s="101"/>
@@ -6906,7 +6900,7 @@
       <c r="AG108" s="101"/>
       <c r="AH108" s="102"/>
     </row>
-    <row r="109" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F109" s="69" t="s">
         <v>32</v>
       </c>
@@ -6941,7 +6935,7 @@
       <c r="AG109" s="70"/>
       <c r="AH109" s="94"/>
     </row>
-    <row r="110" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="3:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F110" s="81"/>
       <c r="G110" s="101"/>
       <c r="H110" s="101"/>
@@ -6974,7 +6968,7 @@
       <c r="AG110" s="101"/>
       <c r="AH110" s="102"/>
     </row>
-    <row r="111" spans="3:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="3:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F111" s="70"/>
       <c r="G111" s="70"/>
       <c r="H111" s="70"/>
@@ -7005,7 +6999,7 @@
       <c r="AG111" s="70"/>
       <c r="AH111" s="70"/>
     </row>
-    <row r="112" spans="3:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="3:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F112" s="70" t="s">
         <v>253</v>
       </c>
@@ -7038,7 +7032,7 @@
       <c r="AG112" s="70"/>
       <c r="AH112" s="70"/>
     </row>
-    <row r="113" spans="5:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="5:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F113" s="70"/>
       <c r="G113" s="70"/>
       <c r="H113" s="70"/>
@@ -7069,7 +7063,7 @@
       <c r="AG113" s="70"/>
       <c r="AH113" s="70"/>
     </row>
-    <row r="114" spans="5:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="5:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F114" s="52" t="s">
         <v>25</v>
       </c>
@@ -7104,7 +7098,7 @@
       <c r="AG114" s="54"/>
       <c r="AH114" s="70"/>
     </row>
-    <row r="115" spans="5:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="5:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F115" s="69" t="s">
         <v>26</v>
       </c>
@@ -7139,7 +7133,7 @@
       <c r="AG115" s="100"/>
       <c r="AH115" s="70"/>
     </row>
-    <row r="116" spans="5:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="5:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F116" s="103"/>
       <c r="G116" s="70"/>
       <c r="H116" s="70"/>
@@ -7172,7 +7166,7 @@
       <c r="AG116" s="94"/>
       <c r="AH116" s="70"/>
     </row>
-    <row r="117" spans="5:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="5:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F117" s="81"/>
       <c r="G117" s="101"/>
       <c r="H117" s="101"/>
@@ -7205,7 +7199,7 @@
       <c r="AG117" s="102"/>
       <c r="AH117" s="70"/>
     </row>
-    <row r="118" spans="5:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="5:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F118" s="103" t="s">
         <v>27</v>
       </c>
@@ -7240,7 +7234,7 @@
       <c r="AG118" s="94"/>
       <c r="AH118" s="70"/>
     </row>
-    <row r="119" spans="5:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="5:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F119" s="103"/>
       <c r="G119" s="70"/>
       <c r="H119" s="70"/>
@@ -7273,7 +7267,7 @@
       <c r="AG119" s="94"/>
       <c r="AH119" s="70"/>
     </row>
-    <row r="120" spans="5:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="5:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F120" s="69" t="s">
         <v>28</v>
       </c>
@@ -7308,7 +7302,7 @@
       <c r="AG120" s="100"/>
       <c r="AH120" s="70"/>
     </row>
-    <row r="121" spans="5:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="5:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F121" s="103" t="s">
         <v>29</v>
       </c>
@@ -7343,7 +7337,7 @@
       <c r="AG121" s="94"/>
       <c r="AH121" s="70"/>
     </row>
-    <row r="122" spans="5:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="5:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F122" s="81"/>
       <c r="G122" s="101"/>
       <c r="H122" s="101"/>
@@ -7376,7 +7370,7 @@
       <c r="AG122" s="102"/>
       <c r="AH122" s="70"/>
     </row>
-    <row r="123" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F123" s="19"/>
       <c r="G123" s="19"/>
       <c r="H123" s="19"/>
@@ -7407,7 +7401,7 @@
       <c r="AG123" s="19"/>
       <c r="AH123" s="19"/>
     </row>
-    <row r="124" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E124" s="28" t="str">
         <f>D100&amp;"3."</f>
         <v>3.1.6.3.</v>
@@ -7416,7 +7410,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="125" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F125" s="24" t="s">
         <v>53</v>
       </c>
@@ -7424,41 +7418,41 @@
         <v>261</v>
       </c>
     </row>
-    <row r="126" spans="5:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="5:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F126" s="24"/>
       <c r="G126" s="41" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="127" spans="5:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="5:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F127" s="24"/>
       <c r="G127" s="41" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="128" spans="5:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="5:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F128" s="24"/>
     </row>
-    <row r="129" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F129" s="24"/>
       <c r="G129" s="41" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="130" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F130" s="24"/>
       <c r="G130" s="41" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="131" spans="2:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="2:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B131" s="36"/>
       <c r="C131" s="36"/>
       <c r="D131" s="36"/>
       <c r="E131" s="36"/>
       <c r="AA131" s="41"/>
     </row>
-    <row r="132" spans="2:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="2:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B132" s="36"/>
       <c r="C132" s="36"/>
       <c r="D132" s="36"/>
@@ -7498,7 +7492,7 @@
       <c r="AG132" s="17"/>
       <c r="AH132" s="18"/>
     </row>
-    <row r="133" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B133" s="36"/>
       <c r="C133" s="36"/>
       <c r="D133" s="36"/>
@@ -7539,7 +7533,7 @@
       <c r="AH133" s="100"/>
       <c r="AI133" s="44"/>
     </row>
-    <row r="134" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B134" s="36"/>
       <c r="C134" s="36"/>
       <c r="D134" s="36"/>
@@ -7575,7 +7569,7 @@
       <c r="AG134" s="70"/>
       <c r="AH134" s="94"/>
     </row>
-    <row r="135" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B135" s="36"/>
       <c r="C135" s="36"/>
       <c r="D135" s="36"/>
@@ -7611,7 +7605,7 @@
       <c r="AG135" s="101"/>
       <c r="AH135" s="102"/>
     </row>
-    <row r="136" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G136" s="103" t="s">
         <v>27</v>
       </c>
@@ -7647,7 +7641,7 @@
       <c r="AG136" s="70"/>
       <c r="AH136" s="94"/>
     </row>
-    <row r="137" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G137" s="81"/>
       <c r="H137" s="101"/>
       <c r="I137" s="101"/>
@@ -7677,7 +7671,7 @@
       <c r="AG137" s="101"/>
       <c r="AH137" s="102"/>
     </row>
-    <row r="138" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G138" s="103" t="s">
         <v>28</v>
       </c>
@@ -7713,7 +7707,7 @@
       <c r="AG138" s="70"/>
       <c r="AH138" s="94"/>
     </row>
-    <row r="139" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G139" s="81" t="s">
         <v>29</v>
       </c>
@@ -7745,8 +7739,8 @@
       <c r="AG139" s="101"/>
       <c r="AH139" s="102"/>
     </row>
-    <row r="140" spans="2:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="141" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="2:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="141" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F141" s="24" t="s">
         <v>52</v>
       </c>
@@ -7754,7 +7748,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="142" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B142" s="36"/>
       <c r="C142" s="36"/>
       <c r="D142" s="36"/>
@@ -7763,13 +7757,13 @@
         <v>265</v>
       </c>
     </row>
-    <row r="143" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B143" s="36"/>
       <c r="C143" s="36"/>
       <c r="D143" s="36"/>
       <c r="E143" s="36"/>
     </row>
-    <row r="144" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B144" s="36"/>
       <c r="C144" s="36"/>
       <c r="D144" s="36"/>
@@ -7809,7 +7803,7 @@
       <c r="AG144" s="53"/>
       <c r="AH144" s="54"/>
     </row>
-    <row r="145" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B145" s="36"/>
       <c r="C145" s="36"/>
       <c r="D145" s="36"/>
@@ -7850,7 +7844,7 @@
       <c r="AH145" s="100"/>
       <c r="AI145" s="44"/>
     </row>
-    <row r="146" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B146" s="36"/>
       <c r="C146" s="36"/>
       <c r="D146" s="36"/>
@@ -7884,8 +7878,8 @@
       <c r="AG146" s="101"/>
       <c r="AH146" s="102"/>
     </row>
-    <row r="147" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="148" spans="2:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="148" spans="2:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C148" s="29"/>
       <c r="D148" s="24" t="str">
         <f>$C$7&amp;"7."</f>
@@ -7918,7 +7912,7 @@
       <c r="AA148" s="29"/>
       <c r="AB148" s="29"/>
     </row>
-    <row r="149" spans="2:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="2:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C149" s="29"/>
       <c r="D149" s="24"/>
       <c r="E149" s="24" t="str">
@@ -7952,7 +7946,7 @@
       <c r="AA149" s="29"/>
       <c r="AB149" s="29"/>
     </row>
-    <row r="150" spans="2:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="2:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C150" s="29"/>
       <c r="D150" s="29"/>
       <c r="E150" s="29"/>
@@ -7982,7 +7976,7 @@
       <c r="AA150" s="29"/>
       <c r="AB150" s="29"/>
     </row>
-    <row r="151" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C151" s="29"/>
       <c r="D151" s="29"/>
       <c r="E151" s="29"/>
@@ -8012,7 +8006,7 @@
       <c r="AA151" s="29"/>
       <c r="AB151" s="29"/>
     </row>
-    <row r="152" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C152" s="29"/>
       <c r="D152" s="29"/>
       <c r="E152" s="29"/>
@@ -8044,7 +8038,7 @@
       <c r="AA152" s="29"/>
       <c r="AB152" s="29"/>
     </row>
-    <row r="153" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C153" s="29"/>
       <c r="D153" s="29"/>
       <c r="E153" s="29"/>
@@ -8076,7 +8070,7 @@
       <c r="AA153" s="29"/>
       <c r="AB153" s="29"/>
     </row>
-    <row r="154" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C154" s="29"/>
       <c r="D154" s="29"/>
       <c r="E154" s="29"/>
@@ -8108,7 +8102,7 @@
       <c r="AA154" s="29"/>
       <c r="AB154" s="29"/>
     </row>
-    <row r="155" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C155" s="29"/>
       <c r="D155" s="29"/>
       <c r="E155" s="29"/>
@@ -8140,7 +8134,7 @@
       <c r="AA155" s="29"/>
       <c r="AB155" s="29"/>
     </row>
-    <row r="156" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="2:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C156" s="29"/>
       <c r="D156" s="29"/>
       <c r="E156" s="29"/>
@@ -8172,7 +8166,7 @@
       <c r="AA156" s="29"/>
       <c r="AB156" s="29"/>
     </row>
-    <row r="157" spans="2:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="2:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C157" s="29"/>
       <c r="D157" s="29"/>
       <c r="E157" s="29"/>
@@ -8200,7 +8194,7 @@
       <c r="AA157" s="29"/>
       <c r="AB157" s="29"/>
     </row>
-    <row r="158" spans="2:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="2:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C158" s="29"/>
       <c r="D158" s="29"/>
       <c r="E158" s="24" t="str">
@@ -8233,7 +8227,7 @@
       <c r="AA158" s="29"/>
       <c r="AB158" s="29"/>
     </row>
-    <row r="159" spans="2:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="2:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C159" s="29"/>
       <c r="D159" s="29"/>
       <c r="E159" s="29"/>
@@ -8263,7 +8257,7 @@
       <c r="AA159" s="29"/>
       <c r="AB159" s="29"/>
     </row>
-    <row r="160" spans="2:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="2:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C160" s="29"/>
       <c r="D160" s="29"/>
       <c r="E160" s="29"/>
@@ -8291,7 +8285,7 @@
       <c r="AA160" s="29"/>
       <c r="AB160" s="29"/>
     </row>
-    <row r="161" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C161" s="29"/>
       <c r="D161" s="29"/>
       <c r="E161" s="29"/>
@@ -8329,7 +8323,7 @@
       <c r="AG161" s="53"/>
       <c r="AH161" s="54"/>
     </row>
-    <row r="162" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C162" s="29"/>
       <c r="D162" s="29"/>
       <c r="E162" s="29"/>
@@ -8367,7 +8361,7 @@
       <c r="AG162" s="98"/>
       <c r="AH162" s="100"/>
     </row>
-    <row r="163" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C163" s="29"/>
       <c r="D163" s="29"/>
       <c r="E163" s="29"/>
@@ -8405,7 +8399,7 @@
       <c r="AG163" s="98"/>
       <c r="AH163" s="100"/>
     </row>
-    <row r="164" spans="1:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C164" s="29"/>
       <c r="D164" s="29"/>
       <c r="E164" s="29"/>
@@ -8441,7 +8435,7 @@
       <c r="AG164" s="101"/>
       <c r="AH164" s="102"/>
     </row>
-    <row r="165" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C165" s="29"/>
       <c r="D165" s="29"/>
       <c r="E165" s="29"/>
@@ -8469,7 +8463,7 @@
       <c r="AA165" s="29"/>
       <c r="AB165" s="29"/>
     </row>
-    <row r="166" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C166" s="29"/>
       <c r="D166" s="29"/>
       <c r="E166" s="24" t="str">
@@ -8502,7 +8496,7 @@
       <c r="AA166" s="29"/>
       <c r="AB166" s="29"/>
     </row>
-    <row r="167" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C167" s="29"/>
       <c r="D167" s="29"/>
       <c r="E167" s="77"/>
@@ -8534,7 +8528,7 @@
       <c r="AA167" s="29"/>
       <c r="AB167" s="29"/>
     </row>
-    <row r="168" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C168" s="29"/>
       <c r="D168" s="29"/>
       <c r="E168" s="77"/>
@@ -8564,7 +8558,7 @@
       <c r="AA168" s="29"/>
       <c r="AB168" s="29"/>
     </row>
-    <row r="169" spans="1:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C169" s="29"/>
       <c r="D169" s="29"/>
       <c r="E169" s="77"/>
@@ -8594,7 +8588,7 @@
       <c r="AA169" s="29"/>
       <c r="AB169" s="29"/>
     </row>
-    <row r="170" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C170" s="29"/>
       <c r="D170" s="29"/>
       <c r="E170" s="77"/>
@@ -8624,7 +8618,7 @@
       <c r="AA170" s="29"/>
       <c r="AB170" s="29"/>
     </row>
-    <row r="171" spans="1:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C171" s="29"/>
       <c r="D171" s="29"/>
       <c r="E171" s="77"/>
@@ -8654,7 +8648,7 @@
       <c r="AA171" s="29"/>
       <c r="AB171" s="29"/>
     </row>
-    <row r="172" spans="1:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C172" s="29"/>
       <c r="D172" s="29"/>
       <c r="E172" s="77"/>
@@ -8682,7 +8676,7 @@
       <c r="AA172" s="29"/>
       <c r="AB172" s="29"/>
     </row>
-    <row r="173" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A173" s="41"/>
       <c r="C173" s="29"/>
       <c r="D173" s="29"/>
@@ -8716,7 +8710,7 @@
       <c r="AA173" s="29"/>
       <c r="AB173" s="29"/>
     </row>
-    <row r="174" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A174" s="41"/>
       <c r="C174" s="29"/>
       <c r="D174" s="29"/>
@@ -8758,7 +8752,7 @@
       <c r="AG174" s="17"/>
       <c r="AH174" s="18"/>
     </row>
-    <row r="175" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A175" s="41"/>
       <c r="C175" s="29"/>
       <c r="D175" s="29"/>
@@ -8800,7 +8794,7 @@
       <c r="AG175" s="19"/>
       <c r="AH175" s="20"/>
     </row>
-    <row r="176" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A176" s="41"/>
       <c r="C176" s="29"/>
       <c r="D176" s="29"/>
@@ -8842,7 +8836,7 @@
       <c r="AG176" s="59"/>
       <c r="AH176" s="60"/>
     </row>
-    <row r="177" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A177" s="41"/>
       <c r="C177" s="29"/>
       <c r="D177" s="29"/>
@@ -8877,7 +8871,7 @@
       <c r="AG177" s="19"/>
       <c r="AH177" s="19"/>
     </row>
-    <row r="178" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C178" s="29"/>
       <c r="D178" s="29"/>
       <c r="E178" s="74"/>
@@ -8910,7 +8904,7 @@
       <c r="AA178" s="29"/>
       <c r="AB178" s="29"/>
     </row>
-    <row r="179" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C179" s="29"/>
       <c r="D179" s="29"/>
       <c r="E179" s="74"/>
@@ -8950,7 +8944,7 @@
       <c r="AG179" s="53"/>
       <c r="AH179" s="54"/>
     </row>
-    <row r="180" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C180" s="29"/>
       <c r="D180" s="29"/>
       <c r="E180" s="74"/>
@@ -8991,7 +8985,7 @@
       <c r="AG180" s="21"/>
       <c r="AH180" s="22"/>
     </row>
-    <row r="181" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C181" s="29"/>
       <c r="D181" s="29"/>
       <c r="E181" s="74"/>
@@ -9019,7 +9013,7 @@
       <c r="AA181" s="29"/>
       <c r="AB181" s="29"/>
     </row>
-    <row r="182" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C182" s="29"/>
       <c r="D182" s="29"/>
       <c r="E182" s="74"/>
@@ -9052,7 +9046,7 @@
       <c r="AA182" s="29"/>
       <c r="AB182" s="29"/>
     </row>
-    <row r="183" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C183" s="29"/>
       <c r="D183" s="29"/>
       <c r="E183" s="74"/>
@@ -9092,7 +9086,7 @@
       <c r="AG183" s="17"/>
       <c r="AH183" s="18"/>
     </row>
-    <row r="184" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C184" s="29"/>
       <c r="D184" s="29"/>
       <c r="E184" s="26"/>
@@ -9133,7 +9127,7 @@
       <c r="AG184" s="49"/>
       <c r="AH184" s="50"/>
     </row>
-    <row r="185" spans="1:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C185" s="29"/>
       <c r="D185" s="29"/>
       <c r="E185" s="74"/>
@@ -9171,7 +9165,7 @@
       <c r="AG185" s="44"/>
       <c r="AH185" s="45"/>
     </row>
-    <row r="186" spans="1:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C186" s="29"/>
       <c r="D186" s="29"/>
       <c r="E186" s="74"/>
@@ -9207,7 +9201,7 @@
       <c r="AG186" s="47"/>
       <c r="AH186" s="51"/>
     </row>
-    <row r="187" spans="1:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C187" s="29"/>
       <c r="D187" s="29"/>
       <c r="E187" s="74"/>
@@ -9241,7 +9235,7 @@
       <c r="AG187" s="44"/>
       <c r="AH187" s="44"/>
     </row>
-    <row r="188" spans="1:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C188" s="29"/>
       <c r="D188" s="29"/>
       <c r="E188" s="74"/>
@@ -9280,7 +9274,7 @@
       <c r="AG188" s="44"/>
       <c r="AH188" s="44"/>
     </row>
-    <row r="189" spans="1:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C189" s="29"/>
       <c r="D189" s="29"/>
       <c r="E189" s="74"/>
@@ -9316,7 +9310,7 @@
       <c r="AG189" s="44"/>
       <c r="AH189" s="44"/>
     </row>
-    <row r="190" spans="1:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C190" s="29"/>
       <c r="D190" s="29"/>
       <c r="E190" s="74"/>
@@ -9350,7 +9344,7 @@
       <c r="AG190" s="44"/>
       <c r="AH190" s="44"/>
     </row>
-    <row r="191" spans="1:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C191" s="29"/>
       <c r="D191" s="29"/>
       <c r="E191" s="74"/>
@@ -9389,7 +9383,7 @@
       <c r="AG191" s="44"/>
       <c r="AH191" s="44"/>
     </row>
-    <row r="192" spans="1:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C192" s="29"/>
       <c r="D192" s="29"/>
       <c r="E192" s="74"/>
@@ -9425,7 +9419,7 @@
       <c r="AG192" s="44"/>
       <c r="AH192" s="44"/>
     </row>
-    <row r="193" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C193" s="29"/>
       <c r="D193" s="29"/>
       <c r="E193" s="74"/>
@@ -9461,7 +9455,7 @@
       <c r="AG193" s="44"/>
       <c r="AH193" s="44"/>
     </row>
-    <row r="194" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C194" s="29"/>
       <c r="D194" s="29"/>
       <c r="E194" s="74"/>
@@ -9497,7 +9491,7 @@
       <c r="AG194" s="44"/>
       <c r="AH194" s="44"/>
     </row>
-    <row r="195" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C195" s="29"/>
       <c r="D195" s="29"/>
       <c r="E195" s="74"/>
@@ -9533,7 +9527,7 @@
       <c r="AG195" s="44"/>
       <c r="AH195" s="44"/>
     </row>
-    <row r="196" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C196" s="29"/>
       <c r="D196" s="29"/>
       <c r="E196" s="29"/>
@@ -9561,7 +9555,7 @@
       <c r="AA196" s="29"/>
       <c r="AB196" s="29"/>
     </row>
-    <row r="197" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A197" s="29"/>
       <c r="B197" s="29"/>
       <c r="C197" s="29"/>
@@ -9603,7 +9597,7 @@
       <c r="AH197" s="29"/>
       <c r="AI197" s="29"/>
     </row>
-    <row r="198" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C198" s="42"/>
       <c r="D198" s="42"/>
       <c r="E198" s="63" t="str">
@@ -9614,13 +9608,13 @@
         <v>301</v>
       </c>
     </row>
-    <row r="199" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F199" s="41" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="200" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="201" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="201" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F201" s="63" t="s">
         <v>303</v>
       </c>
@@ -9628,23 +9622,23 @@
         <v>304</v>
       </c>
     </row>
-    <row r="202" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G202" s="41" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="203" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G203" s="41" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="204" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G204" s="41" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="205" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="206" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="206" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F206" s="63" t="s">
         <v>306</v>
       </c>
@@ -9652,13 +9646,13 @@
         <v>307</v>
       </c>
     </row>
-    <row r="207" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G207" s="41" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="208" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="209" spans="5:7" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="209" spans="5:7" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E209" s="63" t="str">
         <f>$D$197&amp;"2."</f>
         <v>3.1.8.2.</v>
@@ -9667,8 +9661,8 @@
         <v>309</v>
       </c>
     </row>
-    <row r="210" spans="5:7" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="211" spans="5:7" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="5:7" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="211" spans="5:7" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F211" s="63" t="str">
         <f>$E$209&amp;"1."</f>
         <v>3.1.8.2.1.</v>
@@ -9677,28 +9671,28 @@
         <v>310</v>
       </c>
     </row>
-    <row r="212" spans="5:7" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="212" spans="5:7" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G212" s="41" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="213" spans="5:7" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="213" spans="5:7" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G213" s="41" t="s">
         <v>312</v>
       </c>
     </row>
-    <row r="214" spans="5:7" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="214" spans="5:7" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G214" s="41" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="215" spans="5:7" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="215" spans="5:7" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G215" s="41" t="s">
         <v>324</v>
       </c>
     </row>
-    <row r="216" spans="5:7" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="217" spans="5:7" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="216" spans="5:7" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="217" spans="5:7" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F217" s="63" t="str">
         <f>$E$209&amp;"2."</f>
         <v>3.1.8.2.2.</v>
@@ -9707,28 +9701,28 @@
         <v>313</v>
       </c>
     </row>
-    <row r="218" spans="5:7" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="218" spans="5:7" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G218" s="41" t="s">
         <v>314</v>
       </c>
     </row>
-    <row r="219" spans="5:7" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="219" spans="5:7" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G219" s="41" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="220" spans="5:7" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="220" spans="5:7" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G220" s="41" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="221" spans="5:7" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="221" spans="5:7" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G221" s="41" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="222" spans="5:7" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="223" spans="5:7" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="222" spans="5:7" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="223" spans="5:7" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F223" s="63" t="str">
         <f>$E$209&amp;"3."</f>
         <v>3.1.8.2.3.</v>
@@ -9737,23 +9731,23 @@
         <v>318</v>
       </c>
     </row>
-    <row r="224" spans="5:7" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="224" spans="5:7" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G224" s="41" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="225" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G225" s="41" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="226" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G226" s="41" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="227" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="228" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="228" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A228" s="29"/>
       <c r="B228" s="29"/>
       <c r="C228" s="29"/>
@@ -9795,7 +9789,7 @@
       <c r="AH228" s="29"/>
       <c r="AI228" s="29"/>
     </row>
-    <row r="229" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A229" s="29"/>
       <c r="B229" s="29"/>
       <c r="C229" s="29"/>
@@ -9834,7 +9828,7 @@
       <c r="AH229" s="29"/>
       <c r="AI229" s="29"/>
     </row>
-    <row r="230" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A230" s="29"/>
       <c r="B230" s="29"/>
       <c r="C230" s="29"/>
@@ -9871,7 +9865,7 @@
       <c r="AH230" s="29"/>
       <c r="AI230" s="29"/>
     </row>
-    <row r="231" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A231" s="29"/>
       <c r="B231" s="29"/>
       <c r="C231" s="29"/>
@@ -9912,7 +9906,7 @@
       <c r="AH231" s="29"/>
       <c r="AI231" s="29"/>
     </row>
-    <row r="232" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A232" s="29"/>
       <c r="B232" s="29"/>
       <c r="C232" s="29"/>
@@ -9951,7 +9945,7 @@
       <c r="AH232" s="29"/>
       <c r="AI232" s="29"/>
     </row>
-    <row r="233" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A233" s="29"/>
       <c r="B233" s="29"/>
       <c r="C233" s="29"/>
@@ -9994,7 +9988,7 @@
       <c r="AH233" s="37"/>
       <c r="AI233" s="29"/>
     </row>
-    <row r="234" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A234" s="29"/>
       <c r="B234" s="29"/>
       <c r="C234" s="29"/>
@@ -10037,7 +10031,7 @@
       <c r="AH234" s="71"/>
       <c r="AI234" s="29"/>
     </row>
-    <row r="235" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A235" s="29"/>
       <c r="B235" s="29"/>
       <c r="C235" s="29"/>
@@ -10078,7 +10072,7 @@
       <c r="AH235" s="71"/>
       <c r="AI235" s="29"/>
     </row>
-    <row r="236" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A236" s="29"/>
       <c r="B236" s="29"/>
       <c r="C236" s="29"/>
@@ -10117,7 +10111,7 @@
       <c r="AH236" s="71"/>
       <c r="AI236" s="29"/>
     </row>
-    <row r="237" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A237" s="29"/>
       <c r="B237" s="29"/>
       <c r="C237" s="29"/>
@@ -10156,7 +10150,7 @@
       <c r="AH237" s="90"/>
       <c r="AI237" s="29"/>
     </row>
-    <row r="238" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A238" s="29"/>
       <c r="B238" s="29"/>
       <c r="C238" s="29"/>
@@ -10199,7 +10193,7 @@
       <c r="AH238" s="71"/>
       <c r="AI238" s="29"/>
     </row>
-    <row r="239" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A239" s="29"/>
       <c r="B239" s="29"/>
       <c r="C239" s="29"/>
@@ -10240,7 +10234,7 @@
       <c r="AH239" s="71"/>
       <c r="AI239" s="29"/>
     </row>
-    <row r="240" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A240" s="29"/>
       <c r="B240" s="29"/>
       <c r="C240" s="29"/>
@@ -10279,7 +10273,7 @@
       <c r="AH240" s="71"/>
       <c r="AI240" s="29"/>
     </row>
-    <row r="241" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A241" s="29"/>
       <c r="B241" s="29"/>
       <c r="C241" s="29"/>
@@ -10316,7 +10310,7 @@
       <c r="AH241" s="90"/>
       <c r="AI241" s="29"/>
     </row>
-    <row r="242" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A242" s="29"/>
       <c r="B242" s="29"/>
       <c r="C242" s="29"/>
@@ -10359,7 +10353,7 @@
       <c r="AH242" s="71"/>
       <c r="AI242" s="29"/>
     </row>
-    <row r="243" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A243" s="29"/>
       <c r="B243" s="29"/>
       <c r="C243" s="29"/>
@@ -10400,7 +10394,7 @@
       <c r="AH243" s="71"/>
       <c r="AI243" s="29"/>
     </row>
-    <row r="244" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A244" s="29"/>
       <c r="B244" s="29"/>
       <c r="C244" s="29"/>
@@ -10439,7 +10433,7 @@
       <c r="AH244" s="71"/>
       <c r="AI244" s="29"/>
     </row>
-    <row r="245" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A245" s="29"/>
       <c r="B245" s="29"/>
       <c r="C245" s="29"/>
@@ -10478,7 +10472,7 @@
       <c r="AH245" s="71"/>
       <c r="AI245" s="29"/>
     </row>
-    <row r="246" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A246" s="29"/>
       <c r="B246" s="29"/>
       <c r="C246" s="29"/>
@@ -10515,7 +10509,7 @@
       <c r="AH246" s="71"/>
       <c r="AI246" s="29"/>
     </row>
-    <row r="247" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A247" s="29"/>
       <c r="B247" s="29"/>
       <c r="C247" s="29"/>
@@ -10554,7 +10548,7 @@
       <c r="AH247" s="71"/>
       <c r="AI247" s="29"/>
     </row>
-    <row r="248" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A248" s="29"/>
       <c r="B248" s="29"/>
       <c r="C248" s="29"/>
@@ -10593,7 +10587,7 @@
       <c r="AH248" s="71"/>
       <c r="AI248" s="29"/>
     </row>
-    <row r="249" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A249" s="29"/>
       <c r="B249" s="29"/>
       <c r="C249" s="29"/>
@@ -10632,7 +10626,7 @@
       <c r="AH249" s="71"/>
       <c r="AI249" s="29"/>
     </row>
-    <row r="250" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A250" s="29"/>
       <c r="B250" s="29"/>
       <c r="C250" s="29"/>
@@ -10671,7 +10665,7 @@
       <c r="AH250" s="71"/>
       <c r="AI250" s="29"/>
     </row>
-    <row r="251" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A251" s="29"/>
       <c r="B251" s="29"/>
       <c r="C251" s="29"/>
@@ -10710,7 +10704,7 @@
       <c r="AH251" s="71"/>
       <c r="AI251" s="29"/>
     </row>
-    <row r="252" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A252" s="29"/>
       <c r="B252" s="29"/>
       <c r="C252" s="29"/>
@@ -10749,7 +10743,7 @@
       <c r="AH252" s="71"/>
       <c r="AI252" s="29"/>
     </row>
-    <row r="253" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A253" s="29"/>
       <c r="B253" s="29"/>
       <c r="C253" s="29"/>
@@ -10788,7 +10782,7 @@
       <c r="AH253" s="90"/>
       <c r="AI253" s="29"/>
     </row>
-    <row r="254" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A254" s="29"/>
       <c r="B254" s="29"/>
       <c r="C254" s="29"/>
@@ -10831,7 +10825,7 @@
       <c r="AH254" s="71"/>
       <c r="AI254" s="29"/>
     </row>
-    <row r="255" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A255" s="29"/>
       <c r="B255" s="29"/>
       <c r="C255" s="29"/>
@@ -10872,7 +10866,7 @@
       <c r="AH255" s="90"/>
       <c r="AI255" s="29"/>
     </row>
-    <row r="256" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A256" s="29"/>
       <c r="B256" s="29"/>
       <c r="C256" s="29"/>
@@ -10909,7 +10903,7 @@
       <c r="AH256" s="29"/>
       <c r="AI256" s="29"/>
     </row>
-    <row r="257" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A257" s="29"/>
       <c r="B257" s="29"/>
       <c r="C257" s="29"/>
@@ -10950,7 +10944,7 @@
       <c r="AH257" s="29"/>
       <c r="AI257" s="29"/>
     </row>
-    <row r="258" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A258" s="29"/>
       <c r="B258" s="29"/>
       <c r="C258" s="29"/>
@@ -10989,7 +10983,7 @@
       <c r="AH258" s="29"/>
       <c r="AI258" s="29"/>
     </row>
-    <row r="259" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A259" s="29"/>
       <c r="B259" s="29"/>
       <c r="C259" s="29"/>
@@ -11026,7 +11020,7 @@
       <c r="AH259" s="29"/>
       <c r="AI259" s="29"/>
     </row>
-    <row r="260" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A260" s="29"/>
       <c r="B260" s="29"/>
       <c r="C260" s="29"/>
@@ -11068,7 +11062,7 @@
       <c r="AH260" s="29"/>
       <c r="AI260" s="29"/>
     </row>
-    <row r="261" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A261" s="29"/>
       <c r="B261" s="29"/>
       <c r="C261" s="29"/>
@@ -11107,7 +11101,7 @@
       <c r="AH261" s="29"/>
       <c r="AI261" s="29"/>
     </row>
-    <row r="262" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A262" s="29"/>
       <c r="B262" s="29"/>
       <c r="C262" s="29"/>
@@ -11144,7 +11138,7 @@
       <c r="AH262" s="29"/>
       <c r="AI262" s="29"/>
     </row>
-    <row r="263" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A263" s="29"/>
       <c r="B263" s="29"/>
       <c r="C263" s="29"/>
@@ -11185,7 +11179,7 @@
       <c r="AH263" s="29"/>
       <c r="AI263" s="29"/>
     </row>
-    <row r="264" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A264" s="29"/>
       <c r="B264" s="29"/>
       <c r="C264" s="29"/>
@@ -11224,7 +11218,7 @@
       <c r="AH264" s="29"/>
       <c r="AI264" s="29"/>
     </row>
-    <row r="265" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A265" s="29"/>
       <c r="B265" s="29"/>
       <c r="C265" s="29"/>
@@ -11263,7 +11257,7 @@
       <c r="AH265" s="29"/>
       <c r="AI265" s="29"/>
     </row>
-    <row r="266" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A266" s="29"/>
       <c r="B266" s="29"/>
       <c r="C266" s="29"/>
@@ -11302,7 +11296,7 @@
       <c r="AH266" s="29"/>
       <c r="AI266" s="29"/>
     </row>
-    <row r="267" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A267" s="29"/>
       <c r="B267" s="29"/>
       <c r="C267" s="29"/>
@@ -11341,7 +11335,7 @@
       <c r="AH267" s="29"/>
       <c r="AI267" s="29"/>
     </row>
-    <row r="268" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A268" s="29"/>
       <c r="B268" s="29"/>
       <c r="C268" s="29"/>
@@ -11380,7 +11374,7 @@
       <c r="AH268" s="29"/>
       <c r="AI268" s="29"/>
     </row>
-    <row r="269" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A269" s="29"/>
       <c r="B269" s="29"/>
       <c r="C269" s="29"/>
@@ -11417,7 +11411,7 @@
       <c r="AH269" s="29"/>
       <c r="AI269" s="29"/>
     </row>
-    <row r="270" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A270" s="29"/>
       <c r="B270" s="29"/>
       <c r="C270" s="29"/>
@@ -11458,7 +11452,7 @@
       <c r="AH270" s="29"/>
       <c r="AI270" s="29"/>
     </row>
-    <row r="271" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A271" s="29"/>
       <c r="B271" s="29"/>
       <c r="C271" s="29"/>
@@ -11497,7 +11491,7 @@
       <c r="AH271" s="29"/>
       <c r="AI271" s="29"/>
     </row>
-    <row r="272" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A272" s="29"/>
       <c r="B272" s="29"/>
       <c r="C272" s="29"/>
@@ -11536,7 +11530,7 @@
       <c r="AH272" s="29"/>
       <c r="AI272" s="29"/>
     </row>
-    <row r="273" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A273" s="29"/>
       <c r="B273" s="29"/>
       <c r="C273" s="29"/>
@@ -11575,7 +11569,7 @@
       <c r="AH273" s="29"/>
       <c r="AI273" s="29"/>
     </row>
-    <row r="274" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A274" s="29"/>
       <c r="B274" s="29"/>
       <c r="C274" s="29"/>
@@ -11612,7 +11606,7 @@
       <c r="AH274" s="29"/>
       <c r="AI274" s="29"/>
     </row>
-    <row r="275" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A275" s="29"/>
       <c r="B275" s="29"/>
       <c r="C275" s="29"/>
@@ -11651,7 +11645,7 @@
       <c r="AH275" s="29"/>
       <c r="AI275" s="29"/>
     </row>
-    <row r="276" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A276" s="29"/>
       <c r="B276" s="29"/>
       <c r="C276" s="29"/>
@@ -11692,7 +11686,7 @@
       <c r="AH276" s="37"/>
       <c r="AI276" s="29"/>
     </row>
-    <row r="277" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A277" s="29"/>
       <c r="B277" s="29"/>
       <c r="C277" s="29"/>
@@ -11733,7 +11727,7 @@
       <c r="AH277" s="31"/>
       <c r="AI277" s="29"/>
     </row>
-    <row r="278" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A278" s="29"/>
       <c r="B278" s="29"/>
       <c r="C278" s="29"/>
@@ -11772,7 +11766,7 @@
       <c r="AH278" s="34"/>
       <c r="AI278" s="29"/>
     </row>
-    <row r="279" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A279" s="29"/>
       <c r="B279" s="29"/>
       <c r="C279" s="29"/>
@@ -11813,7 +11807,7 @@
       <c r="AH279" s="31"/>
       <c r="AI279" s="29"/>
     </row>
-    <row r="280" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A280" s="29"/>
       <c r="B280" s="29"/>
       <c r="C280" s="29"/>
@@ -11852,7 +11846,7 @@
       <c r="AH280" s="31"/>
       <c r="AI280" s="29"/>
     </row>
-    <row r="281" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A281" s="29"/>
       <c r="B281" s="29"/>
       <c r="C281" s="29"/>
@@ -11891,7 +11885,7 @@
       <c r="AH281" s="34"/>
       <c r="AI281" s="29"/>
     </row>
-    <row r="282" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A282" s="29"/>
       <c r="B282" s="29"/>
       <c r="C282" s="29"/>
@@ -11928,7 +11922,7 @@
       <c r="AH282" s="55"/>
       <c r="AI282" s="29"/>
     </row>
-    <row r="283" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A283" s="29"/>
       <c r="B283" s="29"/>
       <c r="C283" s="29"/>
@@ -11967,7 +11961,7 @@
       <c r="AH283" s="55"/>
       <c r="AI283" s="29"/>
     </row>
-    <row r="284" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A284" s="29"/>
       <c r="B284" s="29"/>
       <c r="C284" s="29"/>
@@ -12004,7 +11998,7 @@
       <c r="AH284" s="55"/>
       <c r="AI284" s="29"/>
     </row>
-    <row r="285" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A285" s="29"/>
       <c r="B285" s="29"/>
       <c r="C285" s="29"/>
@@ -12043,7 +12037,7 @@
       <c r="AH285" s="55"/>
       <c r="AI285" s="29"/>
     </row>
-    <row r="286" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A286" s="29"/>
       <c r="B286" s="29"/>
       <c r="C286" s="29"/>
@@ -12082,7 +12076,7 @@
       <c r="AH286" s="55"/>
       <c r="AI286" s="29"/>
     </row>
-    <row r="287" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A287" s="29"/>
       <c r="B287" s="29"/>
       <c r="C287" s="29"/>
@@ -12119,7 +12113,7 @@
       <c r="AH287" s="55"/>
       <c r="AI287" s="29"/>
     </row>
-    <row r="288" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A288" s="29"/>
       <c r="B288" s="29"/>
       <c r="C288" s="29"/>
@@ -12158,7 +12152,7 @@
       <c r="AH288" s="55"/>
       <c r="AI288" s="29"/>
     </row>
-    <row r="289" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A289" s="29"/>
       <c r="B289" s="29"/>
       <c r="C289" s="29"/>
@@ -12197,7 +12191,7 @@
       <c r="AH289" s="55"/>
       <c r="AI289" s="29"/>
     </row>
-    <row r="290" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A290" s="29"/>
       <c r="B290" s="29"/>
       <c r="C290" s="29"/>
@@ -12236,7 +12230,7 @@
       <c r="AH290" s="55"/>
       <c r="AI290" s="29"/>
     </row>
-    <row r="291" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A291" s="29"/>
       <c r="B291" s="29"/>
       <c r="C291" s="29"/>
@@ -12275,7 +12269,7 @@
       <c r="AH291" s="55"/>
       <c r="AI291" s="29"/>
     </row>
-    <row r="292" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A292" s="29"/>
       <c r="B292" s="29"/>
       <c r="C292" s="29"/>
@@ -12312,7 +12306,7 @@
       <c r="AH292" s="29"/>
       <c r="AI292" s="29"/>
     </row>
-    <row r="293" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D293" s="42" t="str">
         <f>$C$7&amp;"9."</f>
         <v>3.1.9.</v>
@@ -12321,10 +12315,10 @@
         <v>150</v>
       </c>
     </row>
-    <row r="294" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D294" s="42"/>
     </row>
-    <row r="295" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D295" s="42"/>
       <c r="E295" s="42" t="str">
         <f>$D$293&amp;"1."</f>
@@ -12335,13 +12329,13 @@
         <v>URL設計概要</v>
       </c>
     </row>
-    <row r="296" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D296" s="42"/>
       <c r="F296" s="41" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="297" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D297" s="42"/>
       <c r="F297" s="41" t="s">
         <v>148</v>
@@ -12350,10 +12344,10 @@
         <v>147</v>
       </c>
     </row>
-    <row r="298" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D298" s="42"/>
     </row>
-    <row r="299" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D299" s="42"/>
       <c r="E299" s="42" t="str">
         <f>$D$293&amp;"2."</f>
@@ -12364,13 +12358,13 @@
         <v>URL設計方針</v>
       </c>
     </row>
-    <row r="300" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D300" s="42"/>
       <c r="F300" s="41" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="301" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D301" s="42"/>
       <c r="F301" s="52" t="s">
         <v>146</v>
@@ -12405,7 +12399,7 @@
       <c r="AF301" s="53"/>
       <c r="AG301" s="54"/>
     </row>
-    <row r="302" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D302" s="42"/>
       <c r="F302" s="69" t="s">
         <v>145</v>
@@ -12440,7 +12434,7 @@
       <c r="AF302" s="98"/>
       <c r="AG302" s="100"/>
     </row>
-    <row r="303" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D303" s="42"/>
       <c r="F303" s="81"/>
       <c r="G303" s="101"/>
@@ -12473,10 +12467,10 @@
       <c r="AF303" s="101"/>
       <c r="AG303" s="102"/>
     </row>
-    <row r="304" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:35" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D304" s="42"/>
     </row>
-    <row r="305" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="305" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D305" s="42"/>
       <c r="E305" s="42" t="str">
         <f>$D$293&amp;"3."</f>
@@ -12487,7 +12481,7 @@
         <v>URL設計詳細</v>
       </c>
     </row>
-    <row r="306" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="306" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D306" s="42"/>
       <c r="F306" s="29" t="s">
         <v>189</v>
@@ -12495,52 +12489,52 @@
       <c r="G306" s="29"/>
       <c r="H306" s="29"/>
     </row>
-    <row r="307" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="307" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D307" s="42"/>
       <c r="F307" s="29"/>
       <c r="G307" s="29"/>
       <c r="H307" s="29"/>
     </row>
-    <row r="308" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="308" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D308" s="42"/>
       <c r="F308" s="29"/>
       <c r="G308" s="29"/>
       <c r="H308" s="29"/>
     </row>
-    <row r="309" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="309" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D309" s="42"/>
       <c r="F309" s="29"/>
       <c r="G309" s="29"/>
       <c r="H309" s="29"/>
     </row>
-    <row r="310" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="310" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D310" s="42"/>
       <c r="F310" s="29"/>
       <c r="G310" s="29"/>
       <c r="H310" s="29"/>
     </row>
-    <row r="311" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="311" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D311" s="42"/>
       <c r="F311" s="29"/>
       <c r="G311" s="29"/>
       <c r="H311" s="29"/>
     </row>
-    <row r="312" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="312" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D312" s="42"/>
       <c r="F312" s="29"/>
       <c r="G312" s="29"/>
       <c r="H312" s="29"/>
     </row>
-    <row r="313" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="313" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D313" s="42"/>
     </row>
-    <row r="314" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="314" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D314" s="42"/>
     </row>
-    <row r="315" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="315" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D315" s="42"/>
     </row>
-    <row r="316" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="316" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E316" s="42"/>
       <c r="F316" s="87"/>
       <c r="G316" s="52" t="s">
@@ -12574,7 +12568,7 @@
       <c r="AE316" s="53"/>
       <c r="AF316" s="54"/>
     </row>
-    <row r="317" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="317" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E317" s="42"/>
       <c r="F317" s="86" t="s">
         <v>134</v>
@@ -12610,7 +12604,7 @@
       <c r="AE317" s="49"/>
       <c r="AF317" s="50"/>
     </row>
-    <row r="318" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="318" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E318" s="42"/>
       <c r="F318" s="84"/>
       <c r="G318" s="46"/>
@@ -12640,7 +12634,7 @@
       <c r="AE318" s="47"/>
       <c r="AF318" s="51"/>
     </row>
-    <row r="319" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="319" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E319" s="42"/>
       <c r="F319" s="86" t="s">
         <v>132</v>
@@ -12676,7 +12670,7 @@
       <c r="AE319" s="49"/>
       <c r="AF319" s="50"/>
     </row>
-    <row r="320" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="320" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E320" s="42"/>
       <c r="F320" s="84"/>
       <c r="G320" s="46"/>
@@ -12706,7 +12700,7 @@
       <c r="AE320" s="47"/>
       <c r="AF320" s="51"/>
     </row>
-    <row r="321" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="321" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E321" s="42"/>
       <c r="F321" s="86" t="s">
         <v>61</v>
@@ -12742,7 +12736,7 @@
       <c r="AE321" s="49"/>
       <c r="AF321" s="50"/>
     </row>
-    <row r="322" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="322" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E322" s="42"/>
       <c r="F322" s="89"/>
       <c r="G322" s="43"/>
@@ -12774,7 +12768,7 @@
       <c r="AE322" s="44"/>
       <c r="AF322" s="45"/>
     </row>
-    <row r="323" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="323" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E323" s="42"/>
       <c r="F323" s="84"/>
       <c r="G323" s="46"/>
@@ -12804,7 +12798,7 @@
       <c r="AE323" s="47"/>
       <c r="AF323" s="51"/>
     </row>
-    <row r="324" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="324" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E324" s="42"/>
       <c r="F324" s="85" t="s">
         <v>62</v>
@@ -12840,7 +12834,7 @@
       <c r="AE324" s="49"/>
       <c r="AF324" s="50"/>
     </row>
-    <row r="325" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="325" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E325" s="66"/>
       <c r="F325" s="88"/>
       <c r="G325" s="81"/>
@@ -12870,13 +12864,13 @@
       <c r="AE325" s="47"/>
       <c r="AF325" s="51"/>
     </row>
-    <row r="326" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="326" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D326" s="42"/>
       <c r="E326" s="36"/>
       <c r="F326" s="36"/>
       <c r="G326" s="36"/>
     </row>
-    <row r="327" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="327" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D327" s="42"/>
       <c r="E327" s="36"/>
       <c r="F327" s="36" t="s">
@@ -12884,7 +12878,7 @@
       </c>
       <c r="G327" s="36"/>
     </row>
-    <row r="328" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="328" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D328" s="42"/>
       <c r="E328" s="36"/>
       <c r="F328" s="36" t="s">
@@ -12892,12 +12886,12 @@
       </c>
       <c r="G328" s="36"/>
     </row>
-    <row r="329" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="329" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D329" s="42"/>
     </row>
-    <row r="330" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="331" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="332" spans="4:32" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="330" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="331" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="332" spans="4:32" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D332" s="28" t="str">
         <f>$C$7&amp;"10."</f>
         <v>3.1.10.</v>
@@ -12906,7 +12900,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="333" spans="4:32" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="333" spans="4:32" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D333" s="28"/>
       <c r="E333" s="28" t="str">
         <f>D332&amp;"1."</f>
@@ -12917,29 +12911,29 @@
         <v>コンテンツ更新機能概要</v>
       </c>
     </row>
-    <row r="334" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="334" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D334" s="42"/>
       <c r="E334" s="42"/>
       <c r="F334" s="41" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="335" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="335" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D335" s="42"/>
       <c r="E335" s="42"/>
       <c r="F335" s="41" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="336" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="336" spans="4:32" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F336" s="36" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="337" spans="5:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="337" spans="5:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F337" s="36"/>
     </row>
-    <row r="338" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="338" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F338" s="19"/>
       <c r="G338" s="19"/>
       <c r="H338" s="19"/>
@@ -12970,7 +12964,7 @@
       <c r="AG338" s="19"/>
       <c r="AH338" s="19"/>
     </row>
-    <row r="339" spans="5:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="339" spans="5:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E339" s="42" t="str">
         <f>D332&amp;"2."</f>
         <v>3.1.10.2.</v>
@@ -13008,12 +13002,12 @@
       <c r="AG339" s="44"/>
       <c r="AH339" s="44"/>
     </row>
-    <row r="340" spans="5:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="340" spans="5:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F340" s="41" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="341" spans="5:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="341" spans="5:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F341" s="52" t="s">
         <v>50</v>
       </c>
@@ -13050,7 +13044,7 @@
       <c r="AG341" s="53"/>
       <c r="AH341" s="54"/>
     </row>
-    <row r="342" spans="5:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="342" spans="5:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F342" s="81" t="s">
         <v>161</v>
       </c>
@@ -13087,7 +13081,7 @@
       <c r="AG342" s="101"/>
       <c r="AH342" s="102"/>
     </row>
-    <row r="343" spans="5:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="343" spans="5:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F343" s="70"/>
       <c r="G343" s="70"/>
       <c r="H343" s="70"/>
@@ -13118,7 +13112,7 @@
       <c r="AG343" s="44"/>
       <c r="AH343" s="44"/>
     </row>
-    <row r="344" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="344" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E344" s="28" t="str">
         <f>D332&amp;"3."</f>
         <v>3.1.10.3.</v>
@@ -13133,7 +13127,7 @@
       <c r="K344" s="36"/>
       <c r="L344" s="36"/>
     </row>
-    <row r="345" spans="5:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="345" spans="5:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F345" s="77" t="s">
         <v>41</v>
       </c>
@@ -13147,7 +13141,7 @@
       <c r="K345" s="74"/>
       <c r="L345" s="74"/>
     </row>
-    <row r="346" spans="5:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="346" spans="5:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F346" s="77"/>
       <c r="G346" s="79" t="s">
         <v>120</v>
@@ -13160,7 +13154,7 @@
       <c r="K346" s="74"/>
       <c r="L346" s="74"/>
     </row>
-    <row r="347" spans="5:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="347" spans="5:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F347" s="77"/>
       <c r="G347" s="79"/>
       <c r="H347" s="79" t="s">
@@ -13173,7 +13167,7 @@
       <c r="K347" s="74"/>
       <c r="L347" s="74"/>
     </row>
-    <row r="348" spans="5:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="348" spans="5:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F348" s="77"/>
       <c r="G348" s="79" t="s">
         <v>54</v>
@@ -13186,7 +13180,7 @@
       <c r="K348" s="74"/>
       <c r="L348" s="74"/>
     </row>
-    <row r="349" spans="5:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="349" spans="5:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F349" s="77"/>
       <c r="G349" s="74"/>
       <c r="H349" s="79" t="s">
@@ -13199,7 +13193,7 @@
       <c r="K349" s="74"/>
       <c r="L349" s="74"/>
     </row>
-    <row r="350" spans="5:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="350" spans="5:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F350" s="77"/>
       <c r="G350" s="74"/>
       <c r="H350" s="79" t="s">
@@ -13212,7 +13206,7 @@
       <c r="K350" s="74"/>
       <c r="L350" s="74"/>
     </row>
-    <row r="351" spans="5:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="351" spans="5:34" s="29" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F351" s="74"/>
       <c r="G351" s="79" t="s">
         <v>120</v>
@@ -13225,7 +13219,7 @@
       <c r="K351" s="74"/>
       <c r="L351" s="74"/>
     </row>
-    <row r="352" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="352" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F352" s="36"/>
       <c r="G352" s="36"/>
       <c r="H352" s="82" t="s">
@@ -13238,7 +13232,7 @@
       <c r="K352" s="36"/>
       <c r="L352" s="36"/>
     </row>
-    <row r="353" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="353" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F353" s="36"/>
       <c r="G353" s="83"/>
       <c r="H353" s="73" t="s">
@@ -13251,7 +13245,7 @@
       <c r="K353" s="36"/>
       <c r="L353" s="36"/>
     </row>
-    <row r="354" spans="4:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="354" spans="4:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F354" s="36"/>
       <c r="G354" s="83"/>
       <c r="H354" s="36"/>
@@ -13260,7 +13254,7 @@
       <c r="K354" s="36"/>
       <c r="L354" s="36"/>
     </row>
-    <row r="355" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="355" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D355" s="28" t="str">
         <f>$C$7&amp;"11."</f>
         <v>3.1.11.</v>
@@ -13269,7 +13263,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="356" spans="4:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="356" spans="4:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D356" s="42"/>
       <c r="E356" s="42" t="str">
         <f>D355&amp;"1."</f>
@@ -13279,22 +13273,22 @@
         <v>200</v>
       </c>
     </row>
-    <row r="357" spans="4:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="357" spans="4:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D357" s="42"/>
       <c r="E357" s="41" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="358" spans="4:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="358" spans="4:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D358" s="42"/>
       <c r="E358" s="41" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="359" spans="4:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="359" spans="4:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D359" s="42"/>
     </row>
-    <row r="360" spans="4:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="360" spans="4:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D360" s="42"/>
       <c r="E360" s="42" t="str">
         <f>D355&amp;"2."</f>
@@ -13304,13 +13298,13 @@
         <v>201</v>
       </c>
     </row>
-    <row r="361" spans="4:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="361" spans="4:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D361" s="42"/>
       <c r="E361" s="41" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="362" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="362" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F362" s="19"/>
       <c r="G362" s="19"/>
       <c r="H362" s="19"/>
@@ -13341,7 +13335,7 @@
       <c r="AG362" s="19"/>
       <c r="AH362" s="19"/>
     </row>
-    <row r="363" spans="4:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="363" spans="4:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D363" s="42" t="str">
         <f>$C$7&amp;"12."</f>
         <v>3.1.12.</v>
@@ -13350,34 +13344,34 @@
         <v>293</v>
       </c>
     </row>
-    <row r="364" spans="4:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="364" spans="4:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D364" s="42"/>
       <c r="E364" s="41" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="365" spans="4:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="365" spans="4:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D365" s="42"/>
       <c r="E365" s="41" t="s">
         <v>292</v>
       </c>
     </row>
-    <row r="366" spans="4:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="366" spans="4:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D366" s="42"/>
     </row>
-    <row r="367" spans="4:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="367" spans="4:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D367" s="42"/>
       <c r="E367" s="41" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="368" spans="4:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="368" spans="4:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D368" s="42"/>
       <c r="E368" s="41" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="369" spans="6:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="369" spans="6:34" s="41" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F369" s="70"/>
       <c r="G369" s="70"/>
       <c r="H369" s="70"/>
@@ -13408,7 +13402,7 @@
       <c r="AG369" s="44"/>
       <c r="AH369" s="44"/>
     </row>
-    <row r="370" spans="6:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="370" spans="6:34" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F370" s="91"/>
     </row>
   </sheetData>
